--- a/store_dc_distances.xlsx
+++ b/store_dc_distances.xlsx
@@ -453,11 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.8460057247369</v>
+        <v>312.3476429270801</v>
       </c>
     </row>
     <row r="3">
@@ -468,11 +468,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.4928162679067</v>
+        <v>141.5567884198512</v>
       </c>
     </row>
     <row r="4">
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>365.5697738719786</v>
+        <v>375.2133947621184</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>137.1836921009171</v>
+        <v>118.9018437587613</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>370.9274282971861</v>
+        <v>386.3087422339807</v>
       </c>
     </row>
     <row r="7">
@@ -528,11 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135.1668889158399</v>
+        <v>118.9558925056448</v>
       </c>
     </row>
     <row r="8">
@@ -543,11 +543,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>245.074598671275</v>
+        <v>328.2730746713401</v>
       </c>
     </row>
     <row r="9">
@@ -558,11 +558,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>304.8226550499002</v>
+        <v>388.3345797490471</v>
       </c>
     </row>
     <row r="10">
@@ -573,11 +573,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>466.4283882980909</v>
+        <v>485.78077300261</v>
       </c>
     </row>
     <row r="11">
@@ -588,11 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>472.7473727202855</v>
+        <v>492.8602485423139</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>151.0314023786419</v>
+        <v>133.5075553693926</v>
       </c>
     </row>
     <row r="13">
@@ -618,11 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>155.8689391528941</v>
+        <v>138.8671569739272</v>
       </c>
     </row>
     <row r="14">
@@ -633,11 +633,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170.9279161682704</v>
+        <v>153.4618793634799</v>
       </c>
     </row>
     <row r="15">
@@ -648,11 +648,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>413.5495142717604</v>
+        <v>431.3442798376877</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>414.1680610379193</v>
+        <v>424.6636155876099</v>
       </c>
     </row>
     <row r="17">
@@ -678,11 +678,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>155.8711978103603</v>
+        <v>139.2049227489753</v>
       </c>
     </row>
     <row r="18">
@@ -693,11 +693,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>197.3786891663952</v>
+        <v>277.9779084992091</v>
       </c>
     </row>
     <row r="19">
@@ -708,11 +708,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150.8606934652393</v>
+        <v>133.0509347923777</v>
       </c>
     </row>
     <row r="20">
@@ -723,11 +723,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>147.942072551742</v>
+        <v>168.2999938886427</v>
       </c>
     </row>
     <row r="21">
@@ -738,11 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>170.0748304559448</v>
+        <v>241.286644854991</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>274.7525032714101</v>
+        <v>254.3489777477395</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>422.7970840515572</v>
+        <v>439.8981805465693</v>
       </c>
     </row>
     <row r="24">
@@ -783,11 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44.80763566563145</v>
+        <v>114.9129726884635</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>392.7470920930622</v>
+        <v>408.5855438226462</v>
       </c>
     </row>
     <row r="26">
@@ -813,11 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>296.4696464613529</v>
+        <v>379.9781482388589</v>
       </c>
     </row>
     <row r="27">
@@ -828,11 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>162.1806222902383</v>
+        <v>144.8833393517898</v>
       </c>
     </row>
     <row r="28">
@@ -843,11 +843,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>390.3002980085579</v>
+        <v>406.3401413649697</v>
       </c>
     </row>
     <row r="29">
@@ -858,11 +858,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>106.6790260503075</v>
+        <v>183.7395365549781</v>
       </c>
     </row>
     <row r="30">
@@ -873,11 +873,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>260.1363480138145</v>
+        <v>280.1001551232182</v>
       </c>
     </row>
     <row r="31">
@@ -888,11 +888,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>156.190021202696</v>
+        <v>137.9850073898567</v>
       </c>
     </row>
     <row r="32">
@@ -903,11 +903,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160.9219624355327</v>
+        <v>143.1370130472784</v>
       </c>
     </row>
     <row r="33">
@@ -918,11 +918,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>398.7773663232627</v>
+        <v>414.6563633974813</v>
       </c>
     </row>
     <row r="34">
@@ -933,11 +933,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>159.2187052602542</v>
+        <v>231.6252831067762</v>
       </c>
     </row>
     <row r="35">
@@ -948,11 +948,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>159.2061091161018</v>
+        <v>141.5202761549733</v>
       </c>
     </row>
     <row r="36">
@@ -963,11 +963,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>467.3803848016624</v>
+        <v>486.7713001932132</v>
       </c>
     </row>
     <row r="37">
@@ -978,11 +978,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>44.22068792538425</v>
+        <v>115.9067835773086</v>
       </c>
     </row>
     <row r="38">
@@ -993,11 +993,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>155.3531487189899</v>
+        <v>137.8672753703998</v>
       </c>
     </row>
     <row r="39">
@@ -1008,11 +1008,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>384.5306082334927</v>
+        <v>400.3943203558753</v>
       </c>
     </row>
     <row r="40">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>284.4129910582891</v>
+        <v>367.7369200108809</v>
       </c>
     </row>
     <row r="41">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.49259868729828</v>
+        <v>98.15468437307703</v>
       </c>
     </row>
     <row r="42">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>230.7789116574628</v>
+        <v>249.876798128665</v>
       </c>
     </row>
     <row r="43">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>94.04767826631056</v>
+        <v>139.6700844491425</v>
       </c>
     </row>
     <row r="44">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>382.7309042653473</v>
+        <v>392.3383289461026</v>
       </c>
     </row>
     <row r="45">
@@ -1098,11 +1098,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>277.0434321345084</v>
+        <v>360.733750681989</v>
       </c>
     </row>
     <row r="46">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>363.3676583725137</v>
+        <v>380.3280875652389</v>
       </c>
     </row>
     <row r="47">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>367.859288993661</v>
+        <v>384.2953851204009</v>
       </c>
     </row>
     <row r="48">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>148.5993207899491</v>
+        <v>131.7915489876928</v>
       </c>
     </row>
     <row r="49">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>394.3261874511825</v>
+        <v>410.0957017648079</v>
       </c>
     </row>
     <row r="50">
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>466.862664902199</v>
+        <v>486.3552966158776</v>
       </c>
     </row>
     <row r="51">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>244.0476712680346</v>
+        <v>327.371843717464</v>
       </c>
     </row>
     <row r="52">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>105.0335556921193</v>
+        <v>126.6884221680908</v>
       </c>
     </row>
     <row r="53">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>109.7389620112709</v>
+        <v>93.8415059481957</v>
       </c>
     </row>
     <row r="54">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>108.6104453741741</v>
+        <v>176.4470644623666</v>
       </c>
     </row>
     <row r="55">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>164.3915028407905</v>
+        <v>146.7189630432425</v>
       </c>
     </row>
     <row r="56">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>462.2694883273145</v>
+        <v>481.7271018753432</v>
       </c>
     </row>
     <row r="57">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>378.9423803573275</v>
+        <v>399.3315282450388</v>
       </c>
     </row>
     <row r="58">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100.7259767775823</v>
+        <v>108.7848638752269</v>
       </c>
     </row>
     <row r="59">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>165.351606625248</v>
+        <v>147.1540323338647</v>
       </c>
     </row>
     <row r="60">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>155.0573123555761</v>
+        <v>137.4222979025599</v>
       </c>
     </row>
     <row r="61">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>109.6785426341018</v>
+        <v>131.6200947203843</v>
       </c>
     </row>
     <row r="62">
@@ -1353,11 +1353,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>146.6430460690046</v>
+        <v>129.47271130013</v>
       </c>
     </row>
     <row r="63">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>393.1682837749015</v>
+        <v>409.142576533964</v>
       </c>
     </row>
     <row r="64">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>245.079558964301</v>
+        <v>328.2671538715692</v>
       </c>
     </row>
     <row r="65">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>92.73717022738394</v>
+        <v>137.775968778899</v>
       </c>
     </row>
     <row r="66">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>299.3569840336716</v>
+        <v>382.7725994990877</v>
       </c>
     </row>
     <row r="67">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>144.2270060908566</v>
+        <v>127.2148671715527</v>
       </c>
     </row>
     <row r="68">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>103.496349890505</v>
+        <v>187.1173891728598</v>
       </c>
     </row>
     <row r="69">
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68.27692687408248</v>
+        <v>75.96318517921419</v>
       </c>
     </row>
     <row r="70">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>160.2128384245894</v>
+        <v>143.1079901005895</v>
       </c>
     </row>
     <row r="71">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100.7259767775823</v>
+        <v>108.7848638752269</v>
       </c>
     </row>
     <row r="72">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>153.1285040266745</v>
+        <v>136.4020147685627</v>
       </c>
     </row>
     <row r="73">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>409.2001225630211</v>
+        <v>426.8029932126655</v>
       </c>
     </row>
     <row r="74">
@@ -1533,11 +1533,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>151.6020550227136</v>
+        <v>134.4832099001436</v>
       </c>
     </row>
     <row r="75">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>96.58126533093416</v>
+        <v>124.5019625679025</v>
       </c>
     </row>
     <row r="76">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>450.0229442223006</v>
+        <v>468.7426850661527</v>
       </c>
     </row>
     <row r="77">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>103.6119916373755</v>
+        <v>120.9179947370747</v>
       </c>
     </row>
     <row r="78">
@@ -1593,11 +1593,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>190.6825132721265</v>
+        <v>211.1051461597017</v>
       </c>
     </row>
     <row r="79">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>223.9844703950944</v>
+        <v>244.3990735124999</v>
       </c>
     </row>
     <row r="80">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>168.4133991841169</v>
+        <v>151.0245141196881</v>
       </c>
     </row>
     <row r="81">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>159.9084196272836</v>
+        <v>142.94381580362</v>
       </c>
     </row>
     <row r="82">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>155.1193933778405</v>
+        <v>138.2916456117689</v>
       </c>
     </row>
     <row r="83">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>109.7499568719103</v>
+        <v>130.4725566339279</v>
       </c>
     </row>
     <row r="84">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>103.1628998334891</v>
+        <v>128.654547153294</v>
       </c>
     </row>
     <row r="85">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>93.89827386045394</v>
+        <v>137.7742062609717</v>
       </c>
     </row>
     <row r="86">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>154.4089620521199</v>
+        <v>137.1832339917709</v>
       </c>
     </row>
     <row r="87">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>297.954671485222</v>
+        <v>381.4141464317108</v>
       </c>
     </row>
     <row r="88">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>244.9376359487637</v>
+        <v>328.2324482195975</v>
       </c>
     </row>
     <row r="89">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>158.5499688032886</v>
+        <v>141.0311183501512</v>
       </c>
     </row>
     <row r="90">
@@ -1773,11 +1773,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>158.4325457480821</v>
+        <v>141.2722471438568</v>
       </c>
     </row>
     <row r="91">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>150.0773248273609</v>
+        <v>133.2782084515678</v>
       </c>
     </row>
     <row r="92">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>111.1930211145544</v>
+        <v>128.5974961593128</v>
       </c>
     </row>
     <row r="93">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>103.1395370676297</v>
+        <v>126.5993037082896</v>
       </c>
     </row>
     <row r="94">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>157.2643207295644</v>
+        <v>140.2315491170268</v>
       </c>
     </row>
     <row r="95">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>110.9238212584267</v>
+        <v>130.3110932076192</v>
       </c>
     </row>
     <row r="96">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>154.3148811061609</v>
+        <v>136.5442645586296</v>
       </c>
     </row>
     <row r="97">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>160.7866229667267</v>
+        <v>143.4825259368347</v>
       </c>
     </row>
     <row r="98">
@@ -1893,11 +1893,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>153.2436065110408</v>
+        <v>135.7900799156238</v>
       </c>
     </row>
     <row r="99">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>394.5056466031788</v>
+        <v>410.3726253648458</v>
       </c>
     </row>
     <row r="100">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>163.2868500698719</v>
+        <v>145.7555976740724</v>
       </c>
     </row>
     <row r="101">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>150.4724269081669</v>
+        <v>132.978317893762</v>
       </c>
     </row>
     <row r="102">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>140.3539978684227</v>
+        <v>123.4723396428809</v>
       </c>
     </row>
     <row r="103">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>147.6036965257908</v>
+        <v>131.2088258437179</v>
       </c>
     </row>
     <row r="104">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>140.9713963838633</v>
+        <v>123.8725865372433</v>
       </c>
     </row>
     <row r="105">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>382.5222745361521</v>
+        <v>392.2861529735245</v>
       </c>
     </row>
     <row r="106">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>262.7324413613346</v>
+        <v>282.7352857594362</v>
       </c>
     </row>
     <row r="107">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>463.6203705187395</v>
+        <v>483.0990667625962</v>
       </c>
     </row>
     <row r="108">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>390.2487772391969</v>
+        <v>406.0315877170019</v>
       </c>
     </row>
     <row r="109">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>153.539195695105</v>
+        <v>136.4895373399047</v>
       </c>
     </row>
     <row r="110">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>297.4728206135632</v>
+        <v>380.8965900937883</v>
       </c>
     </row>
     <row r="111">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>157.7435654334739</v>
+        <v>140.8386301032752</v>
       </c>
     </row>
     <row r="112">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>146.3339933783038</v>
+        <v>129.4578906436336</v>
       </c>
     </row>
     <row r="113">
@@ -2118,11 +2118,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>149.9757318464934</v>
+        <v>133.6366603171619</v>
       </c>
     </row>
     <row r="114">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>275.4336495404298</v>
+        <v>293.4967601443832</v>
       </c>
     </row>
     <row r="115">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>367.0969959282192</v>
+        <v>380.9416346172154</v>
       </c>
     </row>
     <row r="116">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>143.5474732221657</v>
+        <v>126.9811181546085</v>
       </c>
     </row>
     <row r="117">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>106.0711509208065</v>
+        <v>133.5964249022822</v>
       </c>
     </row>
     <row r="118">
@@ -2193,11 +2193,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>158.0974000785128</v>
+        <v>140.7173414264341</v>
       </c>
     </row>
     <row r="119">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>463.8843261091552</v>
+        <v>483.3104400018008</v>
       </c>
     </row>
     <row r="120">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>297.8104472791561</v>
+        <v>381.2386282180768</v>
       </c>
     </row>
     <row r="121">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>162.1540802945918</v>
+        <v>144.4670761581502</v>
       </c>
     </row>
     <row r="122">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>150.4196753751032</v>
+        <v>133.0423815907709</v>
       </c>
     </row>
     <row r="123">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>40.73116379217367</v>
+        <v>114.1266628728534</v>
       </c>
     </row>
     <row r="124">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>151.2941074551429</v>
+        <v>134.3485696562654</v>
       </c>
     </row>
     <row r="125">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>137.6423599800942</v>
+        <v>120.4872005564761</v>
       </c>
     </row>
     <row r="126">
@@ -2313,11 +2313,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>141.7442910967588</v>
+        <v>125.9371768049107</v>
       </c>
     </row>
     <row r="127">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>152.1140732346485</v>
+        <v>134.3759538513394</v>
       </c>
     </row>
     <row r="128">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>148.417679040193</v>
+        <v>131.3698777549343</v>
       </c>
     </row>
     <row r="129">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>155.2912736366582</v>
+        <v>137.9526950784186</v>
       </c>
     </row>
     <row r="130">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>153.7467056988309</v>
+        <v>136.3894994966892</v>
       </c>
     </row>
     <row r="131">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>68.55822665796128</v>
+        <v>70.25768122189537</v>
       </c>
     </row>
     <row r="132">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>47.08708195175153</v>
+        <v>49.97972614757656</v>
       </c>
     </row>
     <row r="133">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>391.8184530774033</v>
+        <v>407.7414728579811</v>
       </c>
     </row>
     <row r="134">
@@ -2433,11 +2433,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>157.8095881689238</v>
+        <v>140.6749761342152</v>
       </c>
     </row>
     <row r="135">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>171.5590778179512</v>
+        <v>242.8897244503717</v>
       </c>
     </row>
     <row r="136">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>102.338791598857</v>
+        <v>135.8054469712873</v>
       </c>
     </row>
     <row r="137">
@@ -2478,11 +2478,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>105.4461159483704</v>
+        <v>137.3146338603078</v>
       </c>
     </row>
     <row r="138">
@@ -2493,11 +2493,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>154.3020684321744</v>
+        <v>137.5980426536427</v>
       </c>
     </row>
     <row r="139">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>144.0207040191272</v>
+        <v>126.7735021255614</v>
       </c>
     </row>
     <row r="140">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>388.4867996322367</v>
+        <v>404.208875401731</v>
       </c>
     </row>
     <row r="141">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>160.4530529800002</v>
+        <v>143.2619700296298</v>
       </c>
     </row>
     <row r="142">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>279.7075176862222</v>
+        <v>259.3122659168254</v>
       </c>
     </row>
     <row r="143">
@@ -2568,11 +2568,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>137.8802470023848</v>
+        <v>122.5537646253599</v>
       </c>
     </row>
     <row r="144">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>125.8355096270716</v>
+        <v>108.9835170149182</v>
       </c>
     </row>
     <row r="145">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>369.1622100435767</v>
+        <v>382.9364609623582</v>
       </c>
     </row>
     <row r="146">
@@ -2613,11 +2613,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>40.93402369732947</v>
+        <v>112.9323050997713</v>
       </c>
     </row>
     <row r="147">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>146.5562506993173</v>
+        <v>129.9286643047488</v>
       </c>
     </row>
     <row r="148">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>145.0353621763646</v>
+        <v>126.9603102938765</v>
       </c>
     </row>
     <row r="149">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>157.1304892525723</v>
+        <v>139.0718628370146</v>
       </c>
     </row>
     <row r="150">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>121.03539755116</v>
+        <v>104.3207321729001</v>
       </c>
     </row>
     <row r="151">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>378.6092271739076</v>
+        <v>394.1735633146689</v>
       </c>
     </row>
     <row r="152">
@@ -2703,11 +2703,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>453.0618631701936</v>
+        <v>471.6729480562649</v>
       </c>
     </row>
     <row r="153">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>150.9465552515387</v>
+        <v>134.3986826020986</v>
       </c>
     </row>
     <row r="154">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>26.39503825315914</v>
+        <v>100.2591398725851</v>
       </c>
     </row>
     <row r="155">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>139.6648102466222</v>
+        <v>122.8495905764372</v>
       </c>
     </row>
     <row r="156">
@@ -2763,11 +2763,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>147.6298806526679</v>
+        <v>130.088061613333</v>
       </c>
     </row>
     <row r="157">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>466.5173357135325</v>
+        <v>485.9871884773702</v>
       </c>
     </row>
     <row r="158">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>378.5505972995411</v>
+        <v>388.4173225360324</v>
       </c>
     </row>
     <row r="159">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>166.3585398305499</v>
+        <v>149.1025029821664</v>
       </c>
     </row>
     <row r="160">
@@ -2823,11 +2823,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>295.1284815246919</v>
+        <v>378.5419582096303</v>
       </c>
     </row>
     <row r="161">
@@ -2838,11 +2838,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>148.430521977768</v>
+        <v>130.6475561507304</v>
       </c>
     </row>
     <row r="162">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>160.9527014377235</v>
+        <v>143.4355450702218</v>
       </c>
     </row>
     <row r="163">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>66.16610374030769</v>
+        <v>68.20923825105052</v>
       </c>
     </row>
     <row r="164">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>403.3770685462418</v>
+        <v>423.5281084764496</v>
       </c>
     </row>
     <row r="165">
@@ -2898,11 +2898,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>369.9360371615572</v>
+        <v>383.5877977344479</v>
       </c>
     </row>
     <row r="166">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>312.3121417069709</v>
+        <v>326.0226848177935</v>
       </c>
     </row>
     <row r="167">
@@ -2928,11 +2928,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>157.9650373618147</v>
+        <v>140.1897991510045</v>
       </c>
     </row>
     <row r="168">
@@ -2943,11 +2943,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>97.45824180501572</v>
+        <v>141.3235570287463</v>
       </c>
     </row>
     <row r="169">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>43.97404253119719</v>
+        <v>55.30319905350883</v>
       </c>
     </row>
     <row r="170">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>140.7851946362896</v>
+        <v>125.1863571233696</v>
       </c>
     </row>
     <row r="171">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>399.5083708833428</v>
+        <v>416.8347839584198</v>
       </c>
     </row>
     <row r="172">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>161.5314469475466</v>
+        <v>144.4377989386378</v>
       </c>
     </row>
     <row r="173">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>152.6882497958964</v>
+        <v>134.3534034235337</v>
       </c>
     </row>
     <row r="174">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>130.9552456548431</v>
+        <v>114.0055451393923</v>
       </c>
     </row>
     <row r="175">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>110.1578374848856</v>
+        <v>124.7308673591305</v>
       </c>
     </row>
     <row r="176">
@@ -3063,11 +3063,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>198.8890780199291</v>
+        <v>279.5492674223455</v>
       </c>
     </row>
     <row r="177">
@@ -3078,11 +3078,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>266.3355288928579</v>
+        <v>286.2681725369665</v>
       </c>
     </row>
     <row r="178">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>387.6774496753766</v>
+        <v>403.3875092325755</v>
       </c>
     </row>
     <row r="179">
@@ -3108,11 +3108,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>143.8721470076325</v>
+        <v>127.4899347416196</v>
       </c>
     </row>
     <row r="180">
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>140.9664354752053</v>
+        <v>161.0626768672974</v>
       </c>
     </row>
     <row r="181">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>142.7213522013847</v>
+        <v>127.0267048232512</v>
       </c>
     </row>
     <row r="182">
@@ -3153,11 +3153,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>156.9633839319166</v>
+        <v>139.3757855483318</v>
       </c>
     </row>
     <row r="183">
@@ -3168,11 +3168,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>156.7968949445768</v>
+        <v>139.1174159018112</v>
       </c>
     </row>
     <row r="184">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>145.3817134522845</v>
+        <v>129.1647804488381</v>
       </c>
     </row>
     <row r="185">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>164.8960223765515</v>
+        <v>147.3991022417724</v>
       </c>
     </row>
     <row r="186">
@@ -3213,11 +3213,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>160.1367601744726</v>
+        <v>143.0036862149796</v>
       </c>
     </row>
     <row r="187">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>94.57825916665728</v>
+        <v>131.8219351489301</v>
       </c>
     </row>
     <row r="188">
@@ -3243,11 +3243,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>149.0413074483496</v>
+        <v>132.0778531307195</v>
       </c>
     </row>
     <row r="189">
@@ -3258,11 +3258,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>105.1204904123371</v>
+        <v>123.3606496386461</v>
       </c>
     </row>
     <row r="190">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>388.2139984601232</v>
+        <v>403.4008878879773</v>
       </c>
     </row>
     <row r="191">
@@ -3288,11 +3288,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>46.05181255247427</v>
+        <v>52.44417237728874</v>
       </c>
     </row>
     <row r="192">
@@ -3303,11 +3303,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>393.715675009759</v>
+        <v>410.8985883498559</v>
       </c>
     </row>
     <row r="193">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>365.5773635412867</v>
+        <v>379.5971643506353</v>
       </c>
     </row>
     <row r="194">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>90.42836908835832</v>
+        <v>139.1021731415539</v>
       </c>
     </row>
     <row r="195">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>132.9341213620754</v>
+        <v>115.6713272323911</v>
       </c>
     </row>
     <row r="196">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>148.6479009466308</v>
+        <v>129.9353063725652</v>
       </c>
     </row>
     <row r="197">
@@ -3378,11 +3378,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>90.66046051512869</v>
+        <v>112.8438318657794</v>
       </c>
     </row>
     <row r="198">
@@ -3393,11 +3393,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>138.4670632375975</v>
+        <v>212.7765634214703</v>
       </c>
     </row>
     <row r="199">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>144.8737354091315</v>
+        <v>128.0801182035454</v>
       </c>
     </row>
     <row r="200">
@@ -3423,11 +3423,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>150.6046320137467</v>
+        <v>133.1566648141351</v>
       </c>
     </row>
     <row r="201">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>141.2826203035115</v>
+        <v>124.8652061847382</v>
       </c>
     </row>
     <row r="202">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>151.6595942303774</v>
+        <v>133.5168727607165</v>
       </c>
     </row>
     <row r="203">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>68.87397011120331</v>
+        <v>20.05921122465895</v>
       </c>
     </row>
     <row r="204">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>125.0677805919528</v>
+        <v>108.2994590509213</v>
       </c>
     </row>
     <row r="205">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>81.78595913441407</v>
+        <v>109.4976212011855</v>
       </c>
     </row>
     <row r="206">
@@ -3513,11 +3513,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>140.0590297326085</v>
+        <v>176.3651706464888</v>
       </c>
     </row>
     <row r="207">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>98.7323172694025</v>
+        <v>133.315265358216</v>
       </c>
     </row>
     <row r="208">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>150.0719903546772</v>
+        <v>170.4833860549217</v>
       </c>
     </row>
     <row r="209">
@@ -3558,11 +3558,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>156.0220450976014</v>
+        <v>138.0374803401048</v>
       </c>
     </row>
     <row r="210">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>168.2216933394938</v>
+        <v>150.5124814610589</v>
       </c>
     </row>
     <row r="211">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>142.4573195186641</v>
+        <v>124.7669286489615</v>
       </c>
     </row>
     <row r="212">
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>87.98069974649448</v>
+        <v>130.7285006445507</v>
       </c>
     </row>
     <row r="213">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>244.4547600179641</v>
+        <v>237.3450700802627</v>
       </c>
     </row>
     <row r="214">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>224.1347950788545</v>
+        <v>142.4209975774765</v>
       </c>
     </row>
     <row r="215">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>383.9683452505717</v>
+        <v>251.3431037068348</v>
       </c>
     </row>
     <row r="216">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>358.6786998752949</v>
+        <v>76.24503928516523</v>
       </c>
     </row>
     <row r="217">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>405.3050657897217</v>
+        <v>265.8952897520346</v>
       </c>
     </row>
     <row r="218">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>343.1529027900015</v>
+        <v>240.9662567092115</v>
       </c>
     </row>
     <row r="219">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>192.2969368458551</v>
+        <v>232.8831422498661</v>
       </c>
     </row>
     <row r="220">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>379.5007289420488</v>
+        <v>247.7738698315432</v>
       </c>
     </row>
     <row r="221">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>170.9482929019636</v>
+        <v>112.6602580518521</v>
       </c>
     </row>
     <row r="222">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>277.5254540437227</v>
+        <v>212.0819758215432</v>
       </c>
     </row>
     <row r="223">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>346.976523051831</v>
+        <v>293.709077172085</v>
       </c>
     </row>
     <row r="224">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>167.7758876733445</v>
+        <v>115.5900301533268</v>
       </c>
     </row>
     <row r="225">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>405.4342490665469</v>
+        <v>271.5611334846315</v>
       </c>
     </row>
     <row r="226">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>342.2257220137689</v>
+        <v>97.24423539040143</v>
       </c>
     </row>
     <row r="227">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>511.3525973892623</v>
+        <v>313.550423294308</v>
       </c>
     </row>
     <row r="228">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>331.1662139980003</v>
+        <v>108.4127441231689</v>
       </c>
     </row>
     <row r="229">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>381.7256943903093</v>
+        <v>250.6758741271072</v>
       </c>
     </row>
     <row r="230">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>357.0246673916196</v>
+        <v>75.04265743794267</v>
       </c>
     </row>
     <row r="231">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>377.0267809314404</v>
+        <v>246.1432344133759</v>
       </c>
     </row>
     <row r="232">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>169.5897000840959</v>
+        <v>114.30192697602</v>
       </c>
     </row>
     <row r="233">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>336.4473247808326</v>
+        <v>111.4629059928046</v>
       </c>
     </row>
     <row r="234">
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>349.4569968094802</v>
+        <v>297.2711195324988</v>
       </c>
     </row>
     <row r="235">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>223.0922603127969</v>
+        <v>139.6136387191068</v>
       </c>
     </row>
     <row r="236">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>172.9088095760513</v>
+        <v>110.9698302473184</v>
       </c>
     </row>
     <row r="237">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>378.5427318889581</v>
+        <v>248.3393938035115</v>
       </c>
     </row>
     <row r="238">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>181.6944955579513</v>
+        <v>178.8354266787257</v>
       </c>
     </row>
     <row r="239">
@@ -4008,11 +4008,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>510.8703195477742</v>
+        <v>312.1361089671532</v>
       </c>
     </row>
     <row r="240">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>353.6441013146468</v>
+        <v>301.6611093529174</v>
       </c>
     </row>
     <row r="241">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>405.779922177717</v>
+        <v>269.1674756142003</v>
       </c>
     </row>
     <row r="242">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>354.4869959095565</v>
+        <v>72.72870510989631</v>
       </c>
     </row>
     <row r="243">
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>378.7680856783614</v>
+        <v>248.0490537632104</v>
       </c>
     </row>
     <row r="244">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>449.7335626017817</v>
+        <v>171.9775088426673</v>
       </c>
     </row>
     <row r="245">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>176.5776307618488</v>
+        <v>106.9333808471959</v>
       </c>
     </row>
     <row r="246">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>341.5759657726773</v>
+        <v>113.2379343681344</v>
       </c>
     </row>
     <row r="247">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>178.9192601996842</v>
+        <v>105.4632331842252</v>
       </c>
     </row>
     <row r="248">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>337.8575499479376</v>
+        <v>114.3491596408315</v>
       </c>
     </row>
     <row r="249">
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>375.1955729779149</v>
+        <v>245.1275395793918</v>
       </c>
     </row>
     <row r="250">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>414.9905506571422</v>
+        <v>260.1915026413278</v>
       </c>
     </row>
     <row r="251">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>449.8968435611127</v>
+        <v>171.6099279259731</v>
       </c>
     </row>
     <row r="252">
@@ -4203,11 +4203,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>128.9049887187745</v>
+        <v>550.2335312616356</v>
       </c>
     </row>
     <row r="253">
@@ -4218,11 +4218,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>199.9453164122694</v>
+        <v>561.5482385892683</v>
       </c>
     </row>
     <row r="254">
@@ -4233,11 +4233,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>295.4992140148996</v>
+        <v>557.0579250598742</v>
       </c>
     </row>
     <row r="255">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>379.6069181231939</v>
+        <v>700.0507512815924</v>
       </c>
     </row>
     <row r="256">
@@ -4263,11 +4263,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>380.258306252376</v>
+        <v>698.2315230580112</v>
       </c>
     </row>
     <row r="257">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>198.7566561597725</v>
+        <v>579.0433028806783</v>
       </c>
     </row>
     <row r="258">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>157.6723325326645</v>
+        <v>509.5702225252728</v>
       </c>
     </row>
     <row r="259">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>403.5081622823314</v>
+        <v>844.261714845871</v>
       </c>
     </row>
     <row r="260">
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>475.9405988279751</v>
+        <v>1046.468721910672</v>
       </c>
     </row>
     <row r="261">
@@ -4338,11 +4338,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>195.7083783065673</v>
+        <v>508.6605462586443</v>
       </c>
     </row>
     <row r="262">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>438.5077834249905</v>
+        <v>996.6799687422387</v>
       </c>
     </row>
     <row r="263">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>188.2066440310786</v>
+        <v>510.4480584785989</v>
       </c>
     </row>
     <row r="264">
@@ -4383,11 +4383,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>190.9071943197909</v>
+        <v>513.2035290608322</v>
       </c>
     </row>
     <row r="265">
@@ -4398,11 +4398,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>405.0565056120583</v>
+        <v>843.5142465454093</v>
       </c>
     </row>
     <row r="266">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>301.8636096550673</v>
+        <v>553.8226352550597</v>
       </c>
     </row>
     <row r="267">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>198.4266612290852</v>
+        <v>576.614965605559</v>
       </c>
     </row>
     <row r="268">
@@ -4443,11 +4443,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>518.4040578096872</v>
+        <v>1085.208121862374</v>
       </c>
     </row>
     <row r="269">
@@ -4458,11 +4458,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>510.6400033426321</v>
+        <v>1074.234516578657</v>
       </c>
     </row>
     <row r="270">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>197.6583203948707</v>
+        <v>548.1254464247796</v>
       </c>
     </row>
     <row r="271">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>200.1952793995961</v>
+        <v>582.3262762458045</v>
       </c>
     </row>
     <row r="272">
@@ -4503,11 +4503,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>215.1429120314576</v>
+        <v>537.2466317410754</v>
       </c>
     </row>
     <row r="273">
@@ -4518,11 +4518,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>189.4037922176628</v>
+        <v>515.9199484804882</v>
       </c>
     </row>
     <row r="274">
@@ -4533,11 +4533,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>198.7324288034695</v>
+        <v>581.0252119959074</v>
       </c>
     </row>
     <row r="275">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>215.2126130343853</v>
+        <v>536.8600299106262</v>
       </c>
     </row>
     <row r="276">
@@ -4563,11 +4563,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>193.0481946178191</v>
+        <v>511.7048207086222</v>
       </c>
     </row>
     <row r="277">
@@ -4578,11 +4578,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>190.414855387531</v>
+        <v>510.6325809729246</v>
       </c>
     </row>
     <row r="278">
@@ -4593,11 +4593,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>197.1251076937621</v>
+        <v>562.142259489176</v>
       </c>
     </row>
     <row r="279">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>189.8007120211021</v>
+        <v>512.6701910738842</v>
       </c>
     </row>
     <row r="280">
@@ -4623,11 +4623,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>474.2739396380379</v>
+        <v>1044.817507221502</v>
       </c>
     </row>
     <row r="281">
@@ -4638,11 +4638,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>106.1462563154388</v>
+        <v>577.4516136517115</v>
       </c>
     </row>
     <row r="282">
@@ -4653,11 +4653,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>189.5541092308563</v>
+        <v>516.5020371147132</v>
       </c>
     </row>
     <row r="283">
@@ -4668,11 +4668,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>297.7463062317671</v>
+        <v>555.6912913684956</v>
       </c>
     </row>
     <row r="284">
@@ -4683,11 +4683,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>295.1508308036504</v>
+        <v>557.0309337825607</v>
       </c>
     </row>
     <row r="285">
@@ -4698,11 +4698,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>195.2004775661288</v>
+        <v>515.1266831373199</v>
       </c>
     </row>
     <row r="286">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>198.792485816512</v>
+        <v>581.1236556189809</v>
       </c>
     </row>
     <row r="287">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>211.7593814876636</v>
+        <v>553.5205715866714</v>
       </c>
     </row>
     <row r="288">
@@ -4743,11 +4743,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>409.3578444052795</v>
+        <v>807.3513364050648</v>
       </c>
     </row>
     <row r="289">
@@ -4758,11 +4758,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>390.9140081015669</v>
+        <v>962.5966753539426</v>
       </c>
     </row>
     <row r="290">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>260.0725060296554</v>
+        <v>195.8294926826765</v>
       </c>
     </row>
     <row r="291">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>478.6929063561986</v>
+        <v>537.9737707618008</v>
       </c>
     </row>
     <row r="292">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>317.4733968405083</v>
+        <v>325.7527379481806</v>
       </c>
     </row>
     <row r="293">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>174.1455252776595</v>
+        <v>213.6074034689326</v>
       </c>
     </row>
     <row r="294">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>483.6949449878604</v>
+        <v>536.0748695206678</v>
       </c>
     </row>
     <row r="295">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>395.2279755294658</v>
+        <v>374.8062599792478</v>
       </c>
     </row>
     <row r="296">
@@ -4863,11 +4863,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>139.904278070824</v>
+        <v>66.89312229177543</v>
       </c>
     </row>
     <row r="297">
@@ -4878,11 +4878,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>518.017243909774</v>
+        <v>497.6277549216953</v>
       </c>
     </row>
     <row r="298">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>171.8836861734805</v>
+        <v>123.1188905675009</v>
       </c>
     </row>
     <row r="299">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>305.6066734773577</v>
+        <v>627.4253330784752</v>
       </c>
     </row>
     <row r="300">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>145.1818212920968</v>
+        <v>61.47167162779635</v>
       </c>
     </row>
     <row r="301">
@@ -4938,11 +4938,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>419.036129462474</v>
+        <v>597.7896412243185</v>
       </c>
     </row>
     <row r="302">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>407.1102990416741</v>
+        <v>615.8969959031837</v>
       </c>
     </row>
     <row r="303">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>295.353133364184</v>
+        <v>616.3496102117134</v>
       </c>
     </row>
     <row r="304">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>302.21659388239</v>
+        <v>618.4095869413236</v>
       </c>
     </row>
     <row r="305">
@@ -4998,11 +4998,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>299.2683693566714</v>
+        <v>616.0961971153129</v>
       </c>
     </row>
     <row r="306">
@@ -5013,11 +5013,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>265.2849324520069</v>
+        <v>200.2053993384051</v>
       </c>
     </row>
     <row r="307">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>234.1539906552349</v>
+        <v>271.365017209034</v>
       </c>
     </row>
     <row r="308">
@@ -5043,11 +5043,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>137.9645027339064</v>
+        <v>62.69887471408907</v>
       </c>
     </row>
     <row r="309">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>213.5800407661942</v>
+        <v>573.8387765074733</v>
       </c>
     </row>
     <row r="310">
@@ -5073,11 +5073,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>505.864554707247</v>
+        <v>485.7432394022453</v>
       </c>
     </row>
     <row r="311">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>140.4766831106095</v>
+        <v>66.0268932691002</v>
       </c>
     </row>
     <row r="312">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>263.2808293594302</v>
+        <v>198.7592680572442</v>
       </c>
     </row>
     <row r="313">
@@ -5118,11 +5118,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>146.8970220930177</v>
+        <v>63.30485937058388</v>
       </c>
     </row>
     <row r="314">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>252.0220765832538</v>
+        <v>171.2780401337388</v>
       </c>
     </row>
     <row r="315">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>290.8446586327354</v>
+        <v>207.2118431361766</v>
       </c>
     </row>
     <row r="316">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>419.8748338969282</v>
+        <v>596.9053902497836</v>
       </c>
     </row>
     <row r="317">
@@ -5178,11 +5178,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>202.3745627430987</v>
+        <v>121.7310041555266</v>
       </c>
     </row>
     <row r="318">
@@ -5193,11 +5193,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>131.3767754580934</v>
+        <v>49.89652576347511</v>
       </c>
     </row>
     <row r="319">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>405.4616480532131</v>
+        <v>617.4279070361644</v>
       </c>
     </row>
     <row r="320">
@@ -5223,11 +5223,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>257.7202175042919</v>
+        <v>575.0112439592498</v>
       </c>
     </row>
     <row r="321">
@@ -5238,11 +5238,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>299.2069770829289</v>
+        <v>619.2269057530879</v>
       </c>
     </row>
     <row r="322">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>225.2118983559744</v>
+        <v>167.0822270632482</v>
       </c>
     </row>
     <row r="323">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>233.1156151535796</v>
+        <v>270.1330052516413</v>
       </c>
     </row>
     <row r="324">
@@ -5283,11 +5283,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>174.6437031880509</v>
+        <v>123.9640433675536</v>
       </c>
     </row>
     <row r="325">
@@ -5298,11 +5298,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>258.0969226234916</v>
+        <v>185.6342827243591</v>
       </c>
     </row>
     <row r="326">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>143.4559287228808</v>
+        <v>59.72511885034409</v>
       </c>
     </row>
     <row r="327">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>298.5405184854939</v>
+        <v>614.1876446764838</v>
       </c>
     </row>
     <row r="328">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>291.9125166681933</v>
+        <v>607.6027114558465</v>
       </c>
     </row>
     <row r="329">
@@ -5358,11 +5358,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>201.6634020843782</v>
+        <v>241.5798000792561</v>
       </c>
     </row>
     <row r="330">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>187.3472114739193</v>
+        <v>218.3636872097339</v>
       </c>
     </row>
     <row r="331">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>306.1498650987936</v>
+        <v>626.661873619375</v>
       </c>
     </row>
     <row r="332">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>240.6553957539271</v>
+        <v>533.6077234554629</v>
       </c>
     </row>
     <row r="333">
@@ -5418,11 +5418,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>305.5297858281983</v>
+        <v>623.878251310231</v>
       </c>
     </row>
     <row r="334">
@@ -5433,11 +5433,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>265.5314730786209</v>
+        <v>201.3426454253737</v>
       </c>
     </row>
     <row r="335">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>115.8620035916273</v>
+        <v>103.1380002652348</v>
       </c>
     </row>
     <row r="336">
@@ -5463,11 +5463,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>325.2162572181462</v>
+        <v>256.7168714137835</v>
       </c>
     </row>
     <row r="337">
@@ -5478,11 +5478,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>176.0201727541978</v>
+        <v>95.76639060961472</v>
       </c>
     </row>
     <row r="338">
@@ -5493,11 +5493,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>242.8334230268776</v>
+        <v>260.3496983421461</v>
       </c>
     </row>
     <row r="339">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>262.5364558361898</v>
+        <v>339.5078169732922</v>
       </c>
     </row>
     <row r="340">
@@ -5523,11 +5523,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>244.4815171214456</v>
+        <v>268.4852574352886</v>
       </c>
     </row>
     <row r="341">
@@ -5538,11 +5538,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>249.0720943022942</v>
+        <v>246.0994041861252</v>
       </c>
     </row>
     <row r="342">
@@ -5553,11 +5553,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>130.0982456924606</v>
+        <v>244.0803400677385</v>
       </c>
     </row>
     <row r="343">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>244.7649577139401</v>
+        <v>265.1235430500931</v>
       </c>
     </row>
     <row r="344">
@@ -5583,11 +5583,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>170.4849151475579</v>
+        <v>220.5164664270967</v>
       </c>
     </row>
     <row r="345">
@@ -5598,11 +5598,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>247.3589627515343</v>
+        <v>266.4253604948988</v>
       </c>
     </row>
     <row r="346">
@@ -5613,11 +5613,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>250.7518419947306</v>
+        <v>262.1499381849978</v>
       </c>
     </row>
     <row r="347">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>245.2020554131428</v>
+        <v>256.6376844413774</v>
       </c>
     </row>
     <row r="348">
@@ -5643,11 +5643,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>247.1939855447183</v>
+        <v>272.121281660024</v>
       </c>
     </row>
     <row r="349">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>248.9481718440073</v>
+        <v>123.9955394119936</v>
       </c>
     </row>
     <row r="350">
@@ -5673,11 +5673,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>262.8258537407512</v>
+        <v>338.753579945603</v>
       </c>
     </row>
     <row r="351">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>243.9905079930992</v>
+        <v>244.9481478563077</v>
       </c>
     </row>
     <row r="352">
@@ -5703,11 +5703,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>245.7263957483557</v>
+        <v>128.1288650973908</v>
       </c>
     </row>
     <row r="353">
@@ -5718,11 +5718,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>241.3758450983825</v>
+        <v>270.1477232966168</v>
       </c>
     </row>
     <row r="354">
@@ -5733,11 +5733,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>173.6480917764453</v>
+        <v>224.5097660238579</v>
       </c>
     </row>
     <row r="355">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>255.3696671481475</v>
+        <v>319.9119139195989</v>
       </c>
     </row>
     <row r="356">
@@ -5763,11 +5763,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>245.2199955591135</v>
+        <v>127.30602726443</v>
       </c>
     </row>
     <row r="357">
@@ -5778,11 +5778,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>127.1680167975757</v>
+        <v>247.0030921458697</v>
       </c>
     </row>
     <row r="358">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>251.8859543154234</v>
+        <v>245.8723846358603</v>
       </c>
     </row>
     <row r="359">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>244.6616573423616</v>
+        <v>259.1175712553428</v>
       </c>
     </row>
     <row r="360">
@@ -5823,11 +5823,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>242.2130875979642</v>
+        <v>267.5215536520797</v>
       </c>
     </row>
     <row r="361">
@@ -5838,11 +5838,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>184.1323231692768</v>
+        <v>394.2085802884727</v>
       </c>
     </row>
     <row r="362">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>247.2555998483565</v>
+        <v>269.2177499230888</v>
       </c>
     </row>
     <row r="363">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>248.2500861193687</v>
+        <v>265.7120377715198</v>
       </c>
     </row>
     <row r="364">
@@ -5883,11 +5883,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>238.6138624870473</v>
+        <v>272.0407614309759</v>
       </c>
     </row>
     <row r="365">
@@ -5898,11 +5898,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>248.2464578486703</v>
+        <v>267.1609274923284</v>
       </c>
     </row>
     <row r="366">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>251.572927532271</v>
+        <v>119.9739091585612</v>
       </c>
     </row>
     <row r="367">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>230.4299203347763</v>
+        <v>393.9184922121719</v>
       </c>
     </row>
     <row r="368">
@@ -5943,11 +5943,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>230.0711370582394</v>
+        <v>283.3056721743233</v>
       </c>
     </row>
     <row r="369">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>66.73815255783093</v>
+        <v>755.4364692614545</v>
       </c>
     </row>
     <row r="370">
@@ -5973,11 +5973,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>34.52345300414044</v>
+        <v>737.0602738658094</v>
       </c>
     </row>
     <row r="371">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>317.946630304663</v>
+        <v>407.9443120675884</v>
       </c>
     </row>
     <row r="372">
@@ -6003,11 +6003,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>176.6888667503275</v>
+        <v>879.9928298660333</v>
       </c>
     </row>
     <row r="373">
@@ -6018,11 +6018,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>63.09525674037218</v>
+        <v>762.9026211265187</v>
       </c>
     </row>
     <row r="374">
@@ -6033,11 +6033,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>67.88592045568444</v>
+        <v>767.4385075145673</v>
       </c>
     </row>
     <row r="375">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>34.2181840897848</v>
+        <v>737.3593294495913</v>
       </c>
     </row>
     <row r="376">
@@ -6063,11 +6063,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>32.70858238462002</v>
+        <v>732.0924029321508</v>
       </c>
     </row>
     <row r="377">
@@ -6078,11 +6078,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>181.5158062914187</v>
+        <v>885.0784624488344</v>
       </c>
     </row>
     <row r="378">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>180.1765995943753</v>
+        <v>883.3096566025587</v>
       </c>
     </row>
     <row r="379">
@@ -6108,11 +6108,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>35.38984638379532</v>
+        <v>736.889207163484</v>
       </c>
     </row>
     <row r="380">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>148.9146243709701</v>
+        <v>844.8787435615096</v>
       </c>
     </row>
     <row r="381">
@@ -6138,11 +6138,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>292.1082656735446</v>
+        <v>455.5450121192576</v>
       </c>
     </row>
     <row r="382">
@@ -6153,11 +6153,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>33.3796757686011</v>
+        <v>734.8010227130336</v>
       </c>
     </row>
     <row r="383">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>31.90591786876936</v>
+        <v>732.5636727352477</v>
       </c>
     </row>
     <row r="384">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>33.24458419572206</v>
+        <v>735.2834981467736</v>
       </c>
     </row>
     <row r="385">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>63.43243743125071</v>
+        <v>763.5216114415061</v>
       </c>
     </row>
     <row r="386">
@@ -6213,11 +6213,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>293.4508617519292</v>
+        <v>453.3744570574661</v>
       </c>
     </row>
     <row r="387">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>37.08142664821583</v>
+        <v>739.4024454744151</v>
       </c>
     </row>
     <row r="388">
@@ -6243,11 +6243,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>29.33806901372546</v>
+        <v>728.3554642433388</v>
       </c>
     </row>
     <row r="389">
@@ -6258,11 +6258,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>28.37001636872408</v>
+        <v>728.7075752636654</v>
       </c>
     </row>
     <row r="390">
@@ -6273,11 +6273,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>39.11561759641163</v>
+        <v>738.2112070147015</v>
       </c>
     </row>
     <row r="391">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>203.8019484784353</v>
+        <v>909.2151633942545</v>
       </c>
     </row>
     <row r="392">
@@ -6303,11 +6303,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>31.02089893886271</v>
+        <v>730.4862665823251</v>
       </c>
     </row>
     <row r="393">
@@ -6318,11 +6318,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>184.6131265113243</v>
+        <v>887.7534123901355</v>
       </c>
     </row>
     <row r="394">
@@ -6333,11 +6333,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>27.58568935880062</v>
+        <v>725.6101542216179</v>
       </c>
     </row>
     <row r="395">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>30.56895919515435</v>
+        <v>715.8419916078705</v>
       </c>
     </row>
     <row r="396">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>599.7685658275938</v>
+        <v>707.3848536348678</v>
       </c>
     </row>
     <row r="397">
@@ -6378,11 +6378,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>418.910619457074</v>
+        <v>402.8528284779557</v>
       </c>
     </row>
     <row r="398">
@@ -6393,11 +6393,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>395.1452104601061</v>
+        <v>318.7461283580383</v>
       </c>
     </row>
     <row r="399">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>580.0655393103883</v>
+        <v>660.8614547036476</v>
       </c>
     </row>
     <row r="400">
@@ -6423,11 +6423,11 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>419.2014824656533</v>
+        <v>415.0220367356314</v>
       </c>
     </row>
     <row r="401">
@@ -6438,11 +6438,11 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>417.7719448167981</v>
+        <v>404.0941521558714</v>
       </c>
     </row>
     <row r="402">
@@ -6453,11 +6453,11 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>290.1088194372147</v>
+        <v>531.9172069611084</v>
       </c>
     </row>
     <row r="403">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>413.7000010176697</v>
+        <v>408.0188493815209</v>
       </c>
     </row>
     <row r="404">
@@ -6483,11 +6483,11 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>286.2644628689006</v>
+        <v>539.6096633611475</v>
       </c>
     </row>
     <row r="405">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>596.4055858326795</v>
+        <v>703.1264574838835</v>
       </c>
     </row>
     <row r="406">
@@ -6513,11 +6513,11 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>667.4815881169878</v>
+        <v>799.0464878757987</v>
       </c>
     </row>
     <row r="407">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>418.0305093436396</v>
+        <v>403.6412926718086</v>
       </c>
     </row>
     <row r="408">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>577.1715434059126</v>
+        <v>658.928053837548</v>
       </c>
     </row>
     <row r="409">
@@ -6558,11 +6558,11 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>291.0608337402675</v>
+        <v>531.1964786528766</v>
       </c>
     </row>
     <row r="410">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>596.9387958350218</v>
+        <v>702.5680044936581</v>
       </c>
     </row>
     <row r="411">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>417.601541343521</v>
+        <v>404.3147527355172</v>
       </c>
     </row>
     <row r="412">
@@ -6603,11 +6603,11 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>592.2228066044695</v>
+        <v>731.1957182903645</v>
       </c>
     </row>
     <row r="413">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>316.9706336802632</v>
+        <v>513.4781853654288</v>
       </c>
     </row>
     <row r="414">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>623.8236912874983</v>
+        <v>691.0893860919261</v>
       </c>
     </row>
     <row r="415">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>631.3880668617128</v>
+        <v>689.0716245778688</v>
       </c>
     </row>
     <row r="416">
@@ -6663,11 +6663,11 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>594.4100784430385</v>
+        <v>733.8647042878714</v>
       </c>
     </row>
     <row r="417">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>620.2615824043411</v>
+        <v>687.9706222615004</v>
       </c>
     </row>
     <row r="418">
@@ -6693,11 +6693,11 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>204.5305974443592</v>
+        <v>471.9688111199325</v>
       </c>
     </row>
     <row r="419">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>110.2827409697895</v>
+        <v>392.8925776521635</v>
       </c>
     </row>
     <row r="420">
@@ -6723,11 +6723,11 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>204.4596365169506</v>
+        <v>468.1659299344697</v>
       </c>
     </row>
     <row r="421">
@@ -6738,11 +6738,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>163.7742200848483</v>
+        <v>437.6301333322829</v>
       </c>
     </row>
     <row r="422">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>208.7913962749197</v>
+        <v>469.3464139810218</v>
       </c>
     </row>
     <row r="423">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>121.5759418094487</v>
+        <v>404.1736028081135</v>
       </c>
     </row>
     <row r="424">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>213.2182452585202</v>
+        <v>475.7548095131403</v>
       </c>
     </row>
     <row r="425">
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>176.2503739454197</v>
+        <v>374.4568889247058</v>
       </c>
     </row>
     <row r="426">
@@ -6813,11 +6813,11 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>231.1188408667959</v>
+        <v>398.5444258603678</v>
       </c>
     </row>
     <row r="427">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>213.4509778017186</v>
+        <v>477.6547662961582</v>
       </c>
     </row>
     <row r="428">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>181.948223952247</v>
+        <v>372.3583100653588</v>
       </c>
     </row>
     <row r="429">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>94.86397367730432</v>
+        <v>376.8661815300433</v>
       </c>
     </row>
     <row r="430">
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>100.5714524373624</v>
+        <v>382.8441201566035</v>
       </c>
     </row>
     <row r="431">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>48.39588948557887</v>
+        <v>330.9711404490843</v>
       </c>
     </row>
     <row r="432">
@@ -6903,11 +6903,11 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>463.4459507527332</v>
+        <v>396.4694872636811</v>
       </c>
     </row>
     <row r="433">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>433.5621327582323</v>
+        <v>548.1075770880702</v>
       </c>
     </row>
     <row r="434">
@@ -6933,11 +6933,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>229.0852832585927</v>
+        <v>338.3448745348402</v>
       </c>
     </row>
     <row r="435">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>172.6159711788848</v>
+        <v>364.9139797676369</v>
       </c>
     </row>
     <row r="436">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>117.7951780549381</v>
+        <v>400.3918586212197</v>
       </c>
     </row>
     <row r="437">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>97.45745982829436</v>
+        <v>379.8599159448746</v>
       </c>
     </row>
     <row r="438">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>101.481381795035</v>
+        <v>383.8761460419659</v>
       </c>
     </row>
     <row r="439">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>510.997654198796</v>
+        <v>523.1538446003622</v>
       </c>
     </row>
     <row r="440">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>429.4902768901852</v>
+        <v>540.4447070157765</v>
       </c>
     </row>
     <row r="441">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>260.2853585002077</v>
+        <v>541.063100766626</v>
       </c>
     </row>
     <row r="442">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>208.5962880424154</v>
+        <v>361.7951034920814</v>
       </c>
     </row>
     <row r="443">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>98.25808763279977</v>
+        <v>379.865662713909</v>
       </c>
     </row>
     <row r="444">
@@ -7083,11 +7083,11 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>208.4277253435319</v>
+        <v>472.3741090501651</v>
       </c>
     </row>
     <row r="445">
@@ -7098,11 +7098,11 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>212.3386261781216</v>
+        <v>478.0656556116565</v>
       </c>
     </row>
     <row r="446">
@@ -7113,11 +7113,11 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>209.6504118209775</v>
+        <v>470.8794772176558</v>
       </c>
     </row>
     <row r="447">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>182.7667459903581</v>
+        <v>376.3643359901362</v>
       </c>
     </row>
     <row r="448">
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>423.5769488863627</v>
+        <v>539.3000932963816</v>
       </c>
     </row>
     <row r="449">
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>95.67790461919937</v>
+        <v>377.8027639282422</v>
       </c>
     </row>
     <row r="450">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>484.1532863787845</v>
+        <v>423.1133016556792</v>
       </c>
     </row>
     <row r="451">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>228.5218675824255</v>
+        <v>398.4308918550063</v>
       </c>
     </row>
     <row r="452">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>102.6353178628117</v>
+        <v>384.5226986211789</v>
       </c>
     </row>
     <row r="453">
@@ -7218,11 +7218,11 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>301.0507133735346</v>
+        <v>289.6683614717405</v>
       </c>
     </row>
     <row r="454">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>386.2146034980639</v>
+        <v>476.671625154577</v>
       </c>
     </row>
     <row r="455">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>97.23843853479993</v>
+        <v>379.2930854802572</v>
       </c>
     </row>
     <row r="456">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>102.4918480857375</v>
+        <v>384.8164371505356</v>
       </c>
     </row>
     <row r="457">
@@ -7278,11 +7278,11 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>207.4009137645875</v>
+        <v>471.1318091223583</v>
       </c>
     </row>
     <row r="458">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>428.9279411296831</v>
+        <v>544.1825747253724</v>
       </c>
     </row>
     <row r="459">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>229.5591365467445</v>
+        <v>399.465320450838</v>
       </c>
     </row>
     <row r="460">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>175.6247251323167</v>
+        <v>369.0119065625322</v>
       </c>
     </row>
     <row r="461">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>175.3296764752763</v>
+        <v>370.650238082961</v>
       </c>
     </row>
     <row r="462">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>51.09998502013926</v>
+        <v>333.6557619236073</v>
       </c>
     </row>
     <row r="463">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>99.97599824829125</v>
+        <v>382.0640370627376</v>
       </c>
     </row>
     <row r="464">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>168.7811319371953</v>
+        <v>362.2230741759088</v>
       </c>
     </row>
     <row r="465">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>211.6732813870892</v>
+        <v>474.2378592001739</v>
       </c>
     </row>
     <row r="466">
@@ -7413,11 +7413,11 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>232.6220725104062</v>
+        <v>401.665465879754</v>
       </c>
     </row>
     <row r="467">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>100.092607826785</v>
+        <v>382.3170143239886</v>
       </c>
     </row>
     <row r="468">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>96.94585824993405</v>
+        <v>379.0448476203267</v>
       </c>
     </row>
     <row r="469">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>178.0547726996159</v>
+        <v>374.9042615607714</v>
       </c>
     </row>
     <row r="470">
@@ -7473,11 +7473,11 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>209.6007710482695</v>
+        <v>473.324159641636</v>
       </c>
     </row>
     <row r="471">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>217.769738655443</v>
+        <v>480.2135545670378</v>
       </c>
     </row>
     <row r="472">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>102.700602997662</v>
+        <v>385.2222955395411</v>
       </c>
     </row>
     <row r="473">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>172.7706883374275</v>
+        <v>367.3860009118215</v>
       </c>
     </row>
     <row r="474">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>429.3340900803877</v>
+        <v>542.1827885381606</v>
       </c>
     </row>
     <row r="475">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>99.365783649566</v>
+        <v>381.8848835748896</v>
       </c>
     </row>
     <row r="476">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>426.3835440125061</v>
+        <v>538.5790438625913</v>
       </c>
     </row>
     <row r="477">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>178.0194198959729</v>
+        <v>368.6459573800726</v>
       </c>
     </row>
     <row r="478">
@@ -7593,11 +7593,11 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>208.9435669676058</v>
+        <v>474.7514143995931</v>
       </c>
     </row>
     <row r="479">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>178.8457234807114</v>
+        <v>373.9469958264402</v>
       </c>
     </row>
     <row r="480">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>107.3145602966586</v>
+        <v>389.8667975757295</v>
       </c>
     </row>
     <row r="481">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>78.34448568653632</v>
+        <v>356.9198182307821</v>
       </c>
     </row>
     <row r="482">
@@ -7653,11 +7653,11 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>494.2465546328309</v>
+        <v>538.4207338192327</v>
       </c>
     </row>
     <row r="483">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>208.6719006944995</v>
+        <v>486.8211826868632</v>
       </c>
     </row>
     <row r="484">
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>173.0380180324195</v>
+        <v>361.6643405946432</v>
       </c>
     </row>
     <row r="485">
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>306.8243085037814</v>
+        <v>401.930851393678</v>
       </c>
     </row>
     <row r="486">
@@ -7713,11 +7713,11 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>509.5008732297528</v>
+        <v>519.2538226536985</v>
       </c>
     </row>
     <row r="487">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>163.7335498059527</v>
+        <v>279.902734174244</v>
       </c>
     </row>
     <row r="488">
@@ -7743,11 +7743,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>482.7255904190506</v>
+        <v>421.8829865894261</v>
       </c>
     </row>
     <row r="489">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>176.3452400412433</v>
+        <v>369.4452532027314</v>
       </c>
     </row>
     <row r="490">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>96.72437721924653</v>
+        <v>378.3849475489089</v>
       </c>
     </row>
     <row r="491">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>482.017426840228</v>
+        <v>421.4524250593868</v>
       </c>
     </row>
     <row r="492">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>228.9300086027407</v>
+        <v>495.327109267422</v>
       </c>
     </row>
     <row r="493">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>144.5352295904483</v>
+        <v>357.2115310266433</v>
       </c>
     </row>
     <row r="494">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>304.1258562519051</v>
+        <v>399.4831107472828</v>
       </c>
     </row>
     <row r="495">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>176.328593549544</v>
+        <v>370.8772421201244</v>
       </c>
     </row>
     <row r="496">
@@ -7863,11 +7863,11 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>345.6396454305997</v>
+        <v>496.2179314352944</v>
       </c>
     </row>
     <row r="497">
@@ -7878,11 +7878,11 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>204.2468831622038</v>
+        <v>508.6165235388352</v>
       </c>
     </row>
     <row r="498">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>78.46596702303529</v>
+        <v>320.0585897987742</v>
       </c>
     </row>
     <row r="499">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>38.42670238202552</v>
+        <v>301.6603319138252</v>
       </c>
     </row>
     <row r="500">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>228.1579527766796</v>
+        <v>399.3228032090287</v>
       </c>
     </row>
     <row r="501">
@@ -7938,11 +7938,11 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>229.1174983035737</v>
+        <v>396.5711271812636</v>
       </c>
     </row>
     <row r="502">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>121.9724126682299</v>
+        <v>403.9857614874821</v>
       </c>
     </row>
     <row r="503">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>229.178044449383</v>
+        <v>399.6670938287053</v>
       </c>
     </row>
     <row r="504">
@@ -7983,11 +7983,11 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>216.9896041973278</v>
+        <v>429.5073032500679</v>
       </c>
     </row>
     <row r="505">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>112.4827109906133</v>
+        <v>394.7884522559071</v>
       </c>
     </row>
   </sheetData>

--- a/store_dc_distances.xlsx
+++ b/store_dc_distances.xlsx
@@ -453,11 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312.3476429270801</v>
+        <v>293.8460057247369</v>
       </c>
     </row>
     <row r="3">
@@ -468,11 +468,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>141.5567884198512</v>
+        <v>122.4928162679067</v>
       </c>
     </row>
     <row r="4">
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>375.2133947621184</v>
+        <v>365.5697738719786</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>118.9018437587613</v>
+        <v>137.1836921009171</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>386.3087422339807</v>
+        <v>370.9274282971861</v>
       </c>
     </row>
     <row r="7">
@@ -528,11 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>118.9558925056448</v>
+        <v>135.1668889158399</v>
       </c>
     </row>
     <row r="8">
@@ -543,11 +543,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>328.2730746713401</v>
+        <v>245.074598671275</v>
       </c>
     </row>
     <row r="9">
@@ -558,11 +558,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>388.3345797490471</v>
+        <v>304.8226550499002</v>
       </c>
     </row>
     <row r="10">
@@ -573,11 +573,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>485.78077300261</v>
+        <v>466.4283882980909</v>
       </c>
     </row>
     <row r="11">
@@ -588,11 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>492.8602485423139</v>
+        <v>472.7473727202855</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>133.5075553693926</v>
+        <v>151.0314023786419</v>
       </c>
     </row>
     <row r="13">
@@ -618,11 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>138.8671569739272</v>
+        <v>155.8689391528941</v>
       </c>
     </row>
     <row r="14">
@@ -633,11 +633,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>153.4618793634799</v>
+        <v>170.9279161682704</v>
       </c>
     </row>
     <row r="15">
@@ -648,11 +648,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>431.3442798376877</v>
+        <v>413.5495142717604</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>424.6636155876099</v>
+        <v>414.1680610379193</v>
       </c>
     </row>
     <row r="17">
@@ -678,11 +678,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>139.2049227489753</v>
+        <v>155.8711978103603</v>
       </c>
     </row>
     <row r="18">
@@ -693,11 +693,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>277.9779084992091</v>
+        <v>197.3786891663952</v>
       </c>
     </row>
     <row r="19">
@@ -708,11 +708,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>133.0509347923777</v>
+        <v>150.8606934652393</v>
       </c>
     </row>
     <row r="20">
@@ -723,11 +723,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>168.2999938886427</v>
+        <v>147.942072551742</v>
       </c>
     </row>
     <row r="21">
@@ -738,11 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>241.286644854991</v>
+        <v>170.0748304559448</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>254.3489777477395</v>
+        <v>274.7525032714101</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>439.8981805465693</v>
+        <v>422.7970840515572</v>
       </c>
     </row>
     <row r="24">
@@ -783,11 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>114.9129726884635</v>
+        <v>44.80763566563145</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>408.5855438226462</v>
+        <v>392.7470920930622</v>
       </c>
     </row>
     <row r="26">
@@ -813,11 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>379.9781482388589</v>
+        <v>296.4696464613529</v>
       </c>
     </row>
     <row r="27">
@@ -828,11 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>144.8833393517898</v>
+        <v>162.1806222902383</v>
       </c>
     </row>
     <row r="28">
@@ -843,11 +843,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>406.3401413649697</v>
+        <v>390.3002980085579</v>
       </c>
     </row>
     <row r="29">
@@ -858,11 +858,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>183.7395365549781</v>
+        <v>106.6790260503075</v>
       </c>
     </row>
     <row r="30">
@@ -873,11 +873,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>280.1001551232182</v>
+        <v>260.1363480138145</v>
       </c>
     </row>
     <row r="31">
@@ -888,11 +888,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>137.9850073898567</v>
+        <v>156.190021202696</v>
       </c>
     </row>
     <row r="32">
@@ -903,11 +903,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>143.1370130472784</v>
+        <v>160.9219624355327</v>
       </c>
     </row>
     <row r="33">
@@ -918,11 +918,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>414.6563633974813</v>
+        <v>398.7773663232627</v>
       </c>
     </row>
     <row r="34">
@@ -933,11 +933,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>231.6252831067762</v>
+        <v>159.2187052602542</v>
       </c>
     </row>
     <row r="35">
@@ -948,11 +948,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>141.5202761549733</v>
+        <v>159.2061091161018</v>
       </c>
     </row>
     <row r="36">
@@ -963,11 +963,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>486.7713001932132</v>
+        <v>467.3803848016624</v>
       </c>
     </row>
     <row r="37">
@@ -978,11 +978,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>115.9067835773086</v>
+        <v>44.22068792538425</v>
       </c>
     </row>
     <row r="38">
@@ -993,11 +993,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>137.8672753703998</v>
+        <v>155.3531487189899</v>
       </c>
     </row>
     <row r="39">
@@ -1008,11 +1008,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>400.3943203558753</v>
+        <v>384.5306082334927</v>
       </c>
     </row>
     <row r="40">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>367.7369200108809</v>
+        <v>284.4129910582891</v>
       </c>
     </row>
     <row r="41">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>98.15468437307703</v>
+        <v>24.49259868729828</v>
       </c>
     </row>
     <row r="42">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>249.876798128665</v>
+        <v>230.7789116574628</v>
       </c>
     </row>
     <row r="43">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>139.6700844491425</v>
+        <v>94.04767826631056</v>
       </c>
     </row>
     <row r="44">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>392.3383289461026</v>
+        <v>382.7309042653473</v>
       </c>
     </row>
     <row r="45">
@@ -1098,11 +1098,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>360.733750681989</v>
+        <v>277.0434321345084</v>
       </c>
     </row>
     <row r="46">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>380.3280875652389</v>
+        <v>363.3676583725137</v>
       </c>
     </row>
     <row r="47">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>384.2953851204009</v>
+        <v>367.859288993661</v>
       </c>
     </row>
     <row r="48">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>131.7915489876928</v>
+        <v>148.5993207899491</v>
       </c>
     </row>
     <row r="49">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>410.0957017648079</v>
+        <v>394.3261874511825</v>
       </c>
     </row>
     <row r="50">
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>486.3552966158776</v>
+        <v>466.862664902199</v>
       </c>
     </row>
     <row r="51">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>327.371843717464</v>
+        <v>244.0476712680346</v>
       </c>
     </row>
     <row r="52">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>126.6884221680908</v>
+        <v>105.0335556921193</v>
       </c>
     </row>
     <row r="53">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>93.8415059481957</v>
+        <v>109.7389620112709</v>
       </c>
     </row>
     <row r="54">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>176.4470644623666</v>
+        <v>108.6104453741741</v>
       </c>
     </row>
     <row r="55">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>146.7189630432425</v>
+        <v>164.3915028407905</v>
       </c>
     </row>
     <row r="56">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>481.7271018753432</v>
+        <v>462.2694883273145</v>
       </c>
     </row>
     <row r="57">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>399.3315282450388</v>
+        <v>378.9423803573275</v>
       </c>
     </row>
     <row r="58">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>108.7848638752269</v>
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="59">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>147.1540323338647</v>
+        <v>165.351606625248</v>
       </c>
     </row>
     <row r="60">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>137.4222979025599</v>
+        <v>155.0573123555761</v>
       </c>
     </row>
     <row r="61">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>131.6200947203843</v>
+        <v>109.6785426341018</v>
       </c>
     </row>
     <row r="62">
@@ -1353,11 +1353,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>129.47271130013</v>
+        <v>146.6430460690046</v>
       </c>
     </row>
     <row r="63">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>409.142576533964</v>
+        <v>393.1682837749015</v>
       </c>
     </row>
     <row r="64">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>328.2671538715692</v>
+        <v>245.079558964301</v>
       </c>
     </row>
     <row r="65">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>137.775968778899</v>
+        <v>92.73717022738394</v>
       </c>
     </row>
     <row r="66">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>382.7725994990877</v>
+        <v>299.3569840336716</v>
       </c>
     </row>
     <row r="67">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>127.2148671715527</v>
+        <v>144.2270060908566</v>
       </c>
     </row>
     <row r="68">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>187.1173891728598</v>
+        <v>103.496349890505</v>
       </c>
     </row>
     <row r="69">
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>75.96318517921419</v>
+        <v>68.27692687408248</v>
       </c>
     </row>
     <row r="70">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>143.1079901005895</v>
+        <v>160.2128384245894</v>
       </c>
     </row>
     <row r="71">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>108.7848638752269</v>
+        <v>100.7259767775823</v>
       </c>
     </row>
     <row r="72">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>136.4020147685627</v>
+        <v>153.1285040266745</v>
       </c>
     </row>
     <row r="73">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>426.8029932126655</v>
+        <v>409.2001225630211</v>
       </c>
     </row>
     <row r="74">
@@ -1533,11 +1533,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>134.4832099001436</v>
+        <v>151.6020550227136</v>
       </c>
     </row>
     <row r="75">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>124.5019625679025</v>
+        <v>96.58126533093416</v>
       </c>
     </row>
     <row r="76">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>468.7426850661527</v>
+        <v>450.0229442223006</v>
       </c>
     </row>
     <row r="77">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>120.9179947370747</v>
+        <v>103.6119916373755</v>
       </c>
     </row>
     <row r="78">
@@ -1593,11 +1593,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>211.1051461597017</v>
+        <v>190.6825132721265</v>
       </c>
     </row>
     <row r="79">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>244.3990735124999</v>
+        <v>223.9844703950944</v>
       </c>
     </row>
     <row r="80">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>151.0245141196881</v>
+        <v>168.4133991841169</v>
       </c>
     </row>
     <row r="81">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>142.94381580362</v>
+        <v>159.9084196272836</v>
       </c>
     </row>
     <row r="82">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>138.2916456117689</v>
+        <v>155.1193933778405</v>
       </c>
     </row>
     <row r="83">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>130.4725566339279</v>
+        <v>109.7499568719103</v>
       </c>
     </row>
     <row r="84">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>128.654547153294</v>
+        <v>103.1628998334891</v>
       </c>
     </row>
     <row r="85">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>137.7742062609717</v>
+        <v>93.89827386045394</v>
       </c>
     </row>
     <row r="86">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>137.1832339917709</v>
+        <v>154.4089620521199</v>
       </c>
     </row>
     <row r="87">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>381.4141464317108</v>
+        <v>297.954671485222</v>
       </c>
     </row>
     <row r="88">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>328.2324482195975</v>
+        <v>244.9376359487637</v>
       </c>
     </row>
     <row r="89">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>141.0311183501512</v>
+        <v>158.5499688032886</v>
       </c>
     </row>
     <row r="90">
@@ -1773,11 +1773,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>141.2722471438568</v>
+        <v>158.4325457480821</v>
       </c>
     </row>
     <row r="91">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>133.2782084515678</v>
+        <v>150.0773248273609</v>
       </c>
     </row>
     <row r="92">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>128.5974961593128</v>
+        <v>111.1930211145544</v>
       </c>
     </row>
     <row r="93">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>126.5993037082896</v>
+        <v>103.1395370676297</v>
       </c>
     </row>
     <row r="94">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>140.2315491170268</v>
+        <v>157.2643207295644</v>
       </c>
     </row>
     <row r="95">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>130.3110932076192</v>
+        <v>110.9238212584267</v>
       </c>
     </row>
     <row r="96">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>136.5442645586296</v>
+        <v>154.3148811061609</v>
       </c>
     </row>
     <row r="97">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>143.4825259368347</v>
+        <v>160.7866229667267</v>
       </c>
     </row>
     <row r="98">
@@ -1893,11 +1893,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>135.7900799156238</v>
+        <v>153.2436065110408</v>
       </c>
     </row>
     <row r="99">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>410.3726253648458</v>
+        <v>394.5056466031788</v>
       </c>
     </row>
     <row r="100">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>145.7555976740724</v>
+        <v>163.2868500698719</v>
       </c>
     </row>
     <row r="101">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>132.978317893762</v>
+        <v>150.4724269081669</v>
       </c>
     </row>
     <row r="102">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>123.4723396428809</v>
+        <v>140.3539978684227</v>
       </c>
     </row>
     <row r="103">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>131.2088258437179</v>
+        <v>147.6036965257908</v>
       </c>
     </row>
     <row r="104">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>123.8725865372433</v>
+        <v>140.9713963838633</v>
       </c>
     </row>
     <row r="105">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>392.2861529735245</v>
+        <v>382.5222745361521</v>
       </c>
     </row>
     <row r="106">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>282.7352857594362</v>
+        <v>262.7324413613346</v>
       </c>
     </row>
     <row r="107">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>483.0990667625962</v>
+        <v>463.6203705187395</v>
       </c>
     </row>
     <row r="108">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>406.0315877170019</v>
+        <v>390.2487772391969</v>
       </c>
     </row>
     <row r="109">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>136.4895373399047</v>
+        <v>153.539195695105</v>
       </c>
     </row>
     <row r="110">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>380.8965900937883</v>
+        <v>297.4728206135632</v>
       </c>
     </row>
     <row r="111">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>140.8386301032752</v>
+        <v>157.7435654334739</v>
       </c>
     </row>
     <row r="112">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>129.4578906436336</v>
+        <v>146.3339933783038</v>
       </c>
     </row>
     <row r="113">
@@ -2118,11 +2118,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>133.6366603171619</v>
+        <v>149.9757318464934</v>
       </c>
     </row>
     <row r="114">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>293.4967601443832</v>
+        <v>275.4336495404298</v>
       </c>
     </row>
     <row r="115">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>380.9416346172154</v>
+        <v>367.0969959282192</v>
       </c>
     </row>
     <row r="116">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>126.9811181546085</v>
+        <v>143.5474732221657</v>
       </c>
     </row>
     <row r="117">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>133.5964249022822</v>
+        <v>106.0711509208065</v>
       </c>
     </row>
     <row r="118">
@@ -2193,11 +2193,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>140.7173414264341</v>
+        <v>158.0974000785128</v>
       </c>
     </row>
     <row r="119">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>483.3104400018008</v>
+        <v>463.8843261091552</v>
       </c>
     </row>
     <row r="120">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>381.2386282180768</v>
+        <v>297.8104472791561</v>
       </c>
     </row>
     <row r="121">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>144.4670761581502</v>
+        <v>162.1540802945918</v>
       </c>
     </row>
     <row r="122">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>133.0423815907709</v>
+        <v>150.4196753751032</v>
       </c>
     </row>
     <row r="123">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>114.1266628728534</v>
+        <v>40.73116379217367</v>
       </c>
     </row>
     <row r="124">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>134.3485696562654</v>
+        <v>151.2941074551429</v>
       </c>
     </row>
     <row r="125">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>120.4872005564761</v>
+        <v>137.6423599800942</v>
       </c>
     </row>
     <row r="126">
@@ -2313,11 +2313,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>125.9371768049107</v>
+        <v>141.7442910967588</v>
       </c>
     </row>
     <row r="127">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>134.3759538513394</v>
+        <v>152.1140732346485</v>
       </c>
     </row>
     <row r="128">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>131.3698777549343</v>
+        <v>148.417679040193</v>
       </c>
     </row>
     <row r="129">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>137.9526950784186</v>
+        <v>155.2912736366582</v>
       </c>
     </row>
     <row r="130">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>136.3894994966892</v>
+        <v>153.7467056988309</v>
       </c>
     </row>
     <row r="131">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>70.25768122189537</v>
+        <v>68.55822665796128</v>
       </c>
     </row>
     <row r="132">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>49.97972614757656</v>
+        <v>47.08708195175153</v>
       </c>
     </row>
     <row r="133">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>407.7414728579811</v>
+        <v>391.8184530774033</v>
       </c>
     </row>
     <row r="134">
@@ -2433,11 +2433,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>140.6749761342152</v>
+        <v>157.8095881689238</v>
       </c>
     </row>
     <row r="135">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>242.8897244503717</v>
+        <v>171.5590778179512</v>
       </c>
     </row>
     <row r="136">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>135.8054469712873</v>
+        <v>102.338791598857</v>
       </c>
     </row>
     <row r="137">
@@ -2478,11 +2478,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>137.3146338603078</v>
+        <v>105.4461159483704</v>
       </c>
     </row>
     <row r="138">
@@ -2493,11 +2493,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>137.5980426536427</v>
+        <v>154.3020684321744</v>
       </c>
     </row>
     <row r="139">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>126.7735021255614</v>
+        <v>144.0207040191272</v>
       </c>
     </row>
     <row r="140">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>404.208875401731</v>
+        <v>388.4867996322367</v>
       </c>
     </row>
     <row r="141">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>143.2619700296298</v>
+        <v>160.4530529800002</v>
       </c>
     </row>
     <row r="142">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>259.3122659168254</v>
+        <v>279.7075176862222</v>
       </c>
     </row>
     <row r="143">
@@ -2568,11 +2568,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>122.5537646253599</v>
+        <v>137.8802470023848</v>
       </c>
     </row>
     <row r="144">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>108.9835170149182</v>
+        <v>125.8355096270716</v>
       </c>
     </row>
     <row r="145">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>382.9364609623582</v>
+        <v>369.1622100435767</v>
       </c>
     </row>
     <row r="146">
@@ -2613,11 +2613,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>112.9323050997713</v>
+        <v>40.93402369732947</v>
       </c>
     </row>
     <row r="147">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>129.9286643047488</v>
+        <v>146.5562506993173</v>
       </c>
     </row>
     <row r="148">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>126.9603102938765</v>
+        <v>145.0353621763646</v>
       </c>
     </row>
     <row r="149">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>139.0718628370146</v>
+        <v>157.1304892525723</v>
       </c>
     </row>
     <row r="150">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>104.3207321729001</v>
+        <v>121.03539755116</v>
       </c>
     </row>
     <row r="151">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>394.1735633146689</v>
+        <v>378.6092271739076</v>
       </c>
     </row>
     <row r="152">
@@ -2703,11 +2703,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>471.6729480562649</v>
+        <v>453.0618631701936</v>
       </c>
     </row>
     <row r="153">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>134.3986826020986</v>
+        <v>150.9465552515387</v>
       </c>
     </row>
     <row r="154">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>100.2591398725851</v>
+        <v>26.39503825315914</v>
       </c>
     </row>
     <row r="155">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>122.8495905764372</v>
+        <v>139.6648102466222</v>
       </c>
     </row>
     <row r="156">
@@ -2763,11 +2763,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>130.088061613333</v>
+        <v>147.6298806526679</v>
       </c>
     </row>
     <row r="157">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>485.9871884773702</v>
+        <v>466.5173357135325</v>
       </c>
     </row>
     <row r="158">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>388.4173225360324</v>
+        <v>378.5505972995411</v>
       </c>
     </row>
     <row r="159">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>149.1025029821664</v>
+        <v>166.3585398305499</v>
       </c>
     </row>
     <row r="160">
@@ -2823,11 +2823,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>378.5419582096303</v>
+        <v>295.1284815246919</v>
       </c>
     </row>
     <row r="161">
@@ -2838,11 +2838,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>130.6475561507304</v>
+        <v>148.430521977768</v>
       </c>
     </row>
     <row r="162">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>143.4355450702218</v>
+        <v>160.9527014377235</v>
       </c>
     </row>
     <row r="163">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>68.20923825105052</v>
+        <v>66.16610374030769</v>
       </c>
     </row>
     <row r="164">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>423.5281084764496</v>
+        <v>403.3770685462418</v>
       </c>
     </row>
     <row r="165">
@@ -2898,11 +2898,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>383.5877977344479</v>
+        <v>369.9360371615572</v>
       </c>
     </row>
     <row r="166">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>326.0226848177935</v>
+        <v>312.3121417069709</v>
       </c>
     </row>
     <row r="167">
@@ -2928,11 +2928,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>140.1897991510045</v>
+        <v>157.9650373618147</v>
       </c>
     </row>
     <row r="168">
@@ -2943,11 +2943,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>141.3235570287463</v>
+        <v>97.45824180501572</v>
       </c>
     </row>
     <row r="169">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>55.30319905350883</v>
+        <v>43.97404253119719</v>
       </c>
     </row>
     <row r="170">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>125.1863571233696</v>
+        <v>140.7851946362896</v>
       </c>
     </row>
     <row r="171">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>416.8347839584198</v>
+        <v>399.5083708833428</v>
       </c>
     </row>
     <row r="172">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>144.4377989386378</v>
+        <v>161.5314469475466</v>
       </c>
     </row>
     <row r="173">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>134.3534034235337</v>
+        <v>152.6882497958964</v>
       </c>
     </row>
     <row r="174">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>114.0055451393923</v>
+        <v>130.9552456548431</v>
       </c>
     </row>
     <row r="175">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>124.7308673591305</v>
+        <v>110.1578374848856</v>
       </c>
     </row>
     <row r="176">
@@ -3063,11 +3063,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>279.5492674223455</v>
+        <v>198.8890780199291</v>
       </c>
     </row>
     <row r="177">
@@ -3078,11 +3078,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>286.2681725369665</v>
+        <v>266.3355288928579</v>
       </c>
     </row>
     <row r="178">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>403.3875092325755</v>
+        <v>387.6774496753766</v>
       </c>
     </row>
     <row r="179">
@@ -3108,11 +3108,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>127.4899347416196</v>
+        <v>143.8721470076325</v>
       </c>
     </row>
     <row r="180">
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>161.0626768672974</v>
+        <v>140.9664354752053</v>
       </c>
     </row>
     <row r="181">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>127.0267048232512</v>
+        <v>142.7213522013847</v>
       </c>
     </row>
     <row r="182">
@@ -3153,11 +3153,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>139.3757855483318</v>
+        <v>156.9633839319166</v>
       </c>
     </row>
     <row r="183">
@@ -3168,11 +3168,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>139.1174159018112</v>
+        <v>156.7968949445768</v>
       </c>
     </row>
     <row r="184">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>129.1647804488381</v>
+        <v>145.3817134522845</v>
       </c>
     </row>
     <row r="185">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>147.3991022417724</v>
+        <v>164.8960223765515</v>
       </c>
     </row>
     <row r="186">
@@ -3213,11 +3213,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>143.0036862149796</v>
+        <v>160.1367601744726</v>
       </c>
     </row>
     <row r="187">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>131.8219351489301</v>
+        <v>94.57825916665728</v>
       </c>
     </row>
     <row r="188">
@@ -3243,11 +3243,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>132.0778531307195</v>
+        <v>149.0413074483496</v>
       </c>
     </row>
     <row r="189">
@@ -3258,11 +3258,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>123.3606496386461</v>
+        <v>105.1204904123371</v>
       </c>
     </row>
     <row r="190">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>403.4008878879773</v>
+        <v>388.2139984601232</v>
       </c>
     </row>
     <row r="191">
@@ -3288,11 +3288,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>52.44417237728874</v>
+        <v>46.05181255247427</v>
       </c>
     </row>
     <row r="192">
@@ -3303,11 +3303,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>410.8985883498559</v>
+        <v>393.715675009759</v>
       </c>
     </row>
     <row r="193">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>379.5971643506353</v>
+        <v>365.5773635412867</v>
       </c>
     </row>
     <row r="194">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>139.1021731415539</v>
+        <v>90.42836908835832</v>
       </c>
     </row>
     <row r="195">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>115.6713272323911</v>
+        <v>132.9341213620754</v>
       </c>
     </row>
     <row r="196">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>129.9353063725652</v>
+        <v>148.6479009466308</v>
       </c>
     </row>
     <row r="197">
@@ -3378,11 +3378,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>112.8438318657794</v>
+        <v>90.66046051512869</v>
       </c>
     </row>
     <row r="198">
@@ -3393,11 +3393,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>212.7765634214703</v>
+        <v>138.4670632375975</v>
       </c>
     </row>
     <row r="199">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>128.0801182035454</v>
+        <v>144.8737354091315</v>
       </c>
     </row>
     <row r="200">
@@ -3423,11 +3423,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>133.1566648141351</v>
+        <v>150.6046320137467</v>
       </c>
     </row>
     <row r="201">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>124.8652061847382</v>
+        <v>141.2826203035115</v>
       </c>
     </row>
     <row r="202">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>133.5168727607165</v>
+        <v>151.6595942303774</v>
       </c>
     </row>
     <row r="203">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>20.05921122465895</v>
+        <v>68.87397011120331</v>
       </c>
     </row>
     <row r="204">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>108.2994590509213</v>
+        <v>125.0677805919528</v>
       </c>
     </row>
     <row r="205">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>109.4976212011855</v>
+        <v>81.78595913441407</v>
       </c>
     </row>
     <row r="206">
@@ -3513,11 +3513,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>176.3651706464888</v>
+        <v>140.0590297326085</v>
       </c>
     </row>
     <row r="207">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>133.315265358216</v>
+        <v>98.7323172694025</v>
       </c>
     </row>
     <row r="208">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>170.4833860549217</v>
+        <v>150.0719903546772</v>
       </c>
     </row>
     <row r="209">
@@ -3558,11 +3558,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>138.0374803401048</v>
+        <v>156.0220450976014</v>
       </c>
     </row>
     <row r="210">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>150.5124814610589</v>
+        <v>168.2216933394938</v>
       </c>
     </row>
     <row r="211">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>124.7669286489615</v>
+        <v>142.4573195186641</v>
       </c>
     </row>
     <row r="212">
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>130.7285006445507</v>
+        <v>87.98069974649448</v>
       </c>
     </row>
     <row r="213">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>237.3450700802627</v>
+        <v>244.4547600179641</v>
       </c>
     </row>
     <row r="214">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>142.4209975774765</v>
+        <v>224.1347950788545</v>
       </c>
     </row>
     <row r="215">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>251.3431037068348</v>
+        <v>383.9683452505717</v>
       </c>
     </row>
     <row r="216">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>76.24503928516523</v>
+        <v>358.6786998752949</v>
       </c>
     </row>
     <row r="217">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>265.8952897520346</v>
+        <v>405.3050657897217</v>
       </c>
     </row>
     <row r="218">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>240.9662567092115</v>
+        <v>343.1529027900015</v>
       </c>
     </row>
     <row r="219">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>232.8831422498661</v>
+        <v>192.2969368458551</v>
       </c>
     </row>
     <row r="220">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>247.7738698315432</v>
+        <v>379.5007289420488</v>
       </c>
     </row>
     <row r="221">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>112.6602580518521</v>
+        <v>170.9482929019636</v>
       </c>
     </row>
     <row r="222">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>212.0819758215432</v>
+        <v>277.5254540437227</v>
       </c>
     </row>
     <row r="223">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>293.709077172085</v>
+        <v>346.976523051831</v>
       </c>
     </row>
     <row r="224">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>115.5900301533268</v>
+        <v>167.7758876733445</v>
       </c>
     </row>
     <row r="225">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>271.5611334846315</v>
+        <v>405.4342490665469</v>
       </c>
     </row>
     <row r="226">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>97.24423539040143</v>
+        <v>342.2257220137689</v>
       </c>
     </row>
     <row r="227">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>313.550423294308</v>
+        <v>511.3525973892623</v>
       </c>
     </row>
     <row r="228">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>108.4127441231689</v>
+        <v>331.1662139980003</v>
       </c>
     </row>
     <row r="229">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>250.6758741271072</v>
+        <v>381.7256943903093</v>
       </c>
     </row>
     <row r="230">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>75.04265743794267</v>
+        <v>357.0246673916196</v>
       </c>
     </row>
     <row r="231">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>246.1432344133759</v>
+        <v>377.0267809314404</v>
       </c>
     </row>
     <row r="232">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>114.30192697602</v>
+        <v>169.5897000840959</v>
       </c>
     </row>
     <row r="233">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>111.4629059928046</v>
+        <v>336.4473247808326</v>
       </c>
     </row>
     <row r="234">
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>297.2711195324988</v>
+        <v>349.4569968094802</v>
       </c>
     </row>
     <row r="235">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>139.6136387191068</v>
+        <v>223.0922603127969</v>
       </c>
     </row>
     <row r="236">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>110.9698302473184</v>
+        <v>172.9088095760513</v>
       </c>
     </row>
     <row r="237">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>248.3393938035115</v>
+        <v>378.5427318889581</v>
       </c>
     </row>
     <row r="238">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>178.8354266787257</v>
+        <v>181.6944955579513</v>
       </c>
     </row>
     <row r="239">
@@ -4008,11 +4008,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>312.1361089671532</v>
+        <v>510.8703195477742</v>
       </c>
     </row>
     <row r="240">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>301.6611093529174</v>
+        <v>353.6441013146468</v>
       </c>
     </row>
     <row r="241">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>269.1674756142003</v>
+        <v>405.779922177717</v>
       </c>
     </row>
     <row r="242">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>72.72870510989631</v>
+        <v>354.4869959095565</v>
       </c>
     </row>
     <row r="243">
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>248.0490537632104</v>
+        <v>378.7680856783614</v>
       </c>
     </row>
     <row r="244">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>171.9775088426673</v>
+        <v>449.7335626017817</v>
       </c>
     </row>
     <row r="245">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>106.9333808471959</v>
+        <v>176.5776307618488</v>
       </c>
     </row>
     <row r="246">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>113.2379343681344</v>
+        <v>341.5759657726773</v>
       </c>
     </row>
     <row r="247">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>105.4632331842252</v>
+        <v>178.9192601996842</v>
       </c>
     </row>
     <row r="248">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>114.3491596408315</v>
+        <v>337.8575499479376</v>
       </c>
     </row>
     <row r="249">
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>245.1275395793918</v>
+        <v>375.1955729779149</v>
       </c>
     </row>
     <row r="250">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>260.1915026413278</v>
+        <v>414.9905506571422</v>
       </c>
     </row>
     <row r="251">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>171.6099279259731</v>
+        <v>449.8968435611127</v>
       </c>
     </row>
     <row r="252">
@@ -4203,11 +4203,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>550.2335312616356</v>
+        <v>128.9049887187745</v>
       </c>
     </row>
     <row r="253">
@@ -4218,11 +4218,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>561.5482385892683</v>
+        <v>199.9453164122694</v>
       </c>
     </row>
     <row r="254">
@@ -4233,11 +4233,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>557.0579250598742</v>
+        <v>295.4992140148996</v>
       </c>
     </row>
     <row r="255">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>700.0507512815924</v>
+        <v>379.6069181231939</v>
       </c>
     </row>
     <row r="256">
@@ -4263,11 +4263,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>698.2315230580112</v>
+        <v>380.258306252376</v>
       </c>
     </row>
     <row r="257">
@@ -4278,11 +4278,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>579.0433028806783</v>
+        <v>198.7566561597725</v>
       </c>
     </row>
     <row r="258">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>509.5702225252728</v>
+        <v>157.6723325326645</v>
       </c>
     </row>
     <row r="259">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>844.261714845871</v>
+        <v>403.5081622823314</v>
       </c>
     </row>
     <row r="260">
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1046.468721910672</v>
+        <v>475.9405988279751</v>
       </c>
     </row>
     <row r="261">
@@ -4338,11 +4338,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>508.6605462586443</v>
+        <v>195.7083783065673</v>
       </c>
     </row>
     <row r="262">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>996.6799687422387</v>
+        <v>438.5077834249905</v>
       </c>
     </row>
     <row r="263">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>510.4480584785989</v>
+        <v>188.2066440310786</v>
       </c>
     </row>
     <row r="264">
@@ -4383,11 +4383,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>513.2035290608322</v>
+        <v>190.9071943197909</v>
       </c>
     </row>
     <row r="265">
@@ -4398,11 +4398,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>843.5142465454093</v>
+        <v>405.0565056120583</v>
       </c>
     </row>
     <row r="266">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>553.8226352550597</v>
+        <v>301.8636096550673</v>
       </c>
     </row>
     <row r="267">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>576.614965605559</v>
+        <v>198.4266612290852</v>
       </c>
     </row>
     <row r="268">
@@ -4443,11 +4443,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1085.208121862374</v>
+        <v>518.4040578096872</v>
       </c>
     </row>
     <row r="269">
@@ -4458,11 +4458,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1074.234516578657</v>
+        <v>510.6400033426321</v>
       </c>
     </row>
     <row r="270">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>548.1254464247796</v>
+        <v>197.6583203948707</v>
       </c>
     </row>
     <row r="271">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>582.3262762458045</v>
+        <v>200.1952793995961</v>
       </c>
     </row>
     <row r="272">
@@ -4503,11 +4503,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>537.2466317410754</v>
+        <v>215.1429120314576</v>
       </c>
     </row>
     <row r="273">
@@ -4518,11 +4518,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>515.9199484804882</v>
+        <v>189.4037922176628</v>
       </c>
     </row>
     <row r="274">
@@ -4533,11 +4533,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>581.0252119959074</v>
+        <v>198.7324288034695</v>
       </c>
     </row>
     <row r="275">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>536.8600299106262</v>
+        <v>215.2126130343853</v>
       </c>
     </row>
     <row r="276">
@@ -4563,11 +4563,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>511.7048207086222</v>
+        <v>193.0481946178191</v>
       </c>
     </row>
     <row r="277">
@@ -4578,11 +4578,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>510.6325809729246</v>
+        <v>190.414855387531</v>
       </c>
     </row>
     <row r="278">
@@ -4593,11 +4593,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>562.142259489176</v>
+        <v>197.1251076937621</v>
       </c>
     </row>
     <row r="279">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>512.6701910738842</v>
+        <v>189.8007120211021</v>
       </c>
     </row>
     <row r="280">
@@ -4623,11 +4623,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>1044.817507221502</v>
+        <v>474.2739396380379</v>
       </c>
     </row>
     <row r="281">
@@ -4638,11 +4638,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>577.4516136517115</v>
+        <v>106.1462563154388</v>
       </c>
     </row>
     <row r="282">
@@ -4653,11 +4653,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>516.5020371147132</v>
+        <v>189.5541092308563</v>
       </c>
     </row>
     <row r="283">
@@ -4668,11 +4668,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>555.6912913684956</v>
+        <v>297.7463062317671</v>
       </c>
     </row>
     <row r="284">
@@ -4683,11 +4683,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>557.0309337825607</v>
+        <v>295.1508308036504</v>
       </c>
     </row>
     <row r="285">
@@ -4698,11 +4698,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>515.1266831373199</v>
+        <v>195.2004775661288</v>
       </c>
     </row>
     <row r="286">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>581.1236556189809</v>
+        <v>198.792485816512</v>
       </c>
     </row>
     <row r="287">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>553.5205715866714</v>
+        <v>211.7593814876636</v>
       </c>
     </row>
     <row r="288">
@@ -4743,11 +4743,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>807.3513364050648</v>
+        <v>409.3578444052795</v>
       </c>
     </row>
     <row r="289">
@@ -4758,11 +4758,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>962.5966753539426</v>
+        <v>390.9140081015669</v>
       </c>
     </row>
     <row r="290">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>195.8294926826765</v>
+        <v>260.0725060296554</v>
       </c>
     </row>
     <row r="291">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>537.9737707618008</v>
+        <v>478.6929063561986</v>
       </c>
     </row>
     <row r="292">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>325.7527379481806</v>
+        <v>317.4733968405083</v>
       </c>
     </row>
     <row r="293">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>213.6074034689326</v>
+        <v>174.1455252776595</v>
       </c>
     </row>
     <row r="294">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>536.0748695206678</v>
+        <v>483.6949449878604</v>
       </c>
     </row>
     <row r="295">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>374.8062599792478</v>
+        <v>395.2279755294658</v>
       </c>
     </row>
     <row r="296">
@@ -4863,11 +4863,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>66.89312229177543</v>
+        <v>139.904278070824</v>
       </c>
     </row>
     <row r="297">
@@ -4878,11 +4878,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>497.6277549216953</v>
+        <v>518.017243909774</v>
       </c>
     </row>
     <row r="298">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>123.1188905675009</v>
+        <v>171.8836861734805</v>
       </c>
     </row>
     <row r="299">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>627.4253330784752</v>
+        <v>305.6066734773577</v>
       </c>
     </row>
     <row r="300">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>61.47167162779635</v>
+        <v>145.1818212920968</v>
       </c>
     </row>
     <row r="301">
@@ -4938,11 +4938,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>597.7896412243185</v>
+        <v>419.036129462474</v>
       </c>
     </row>
     <row r="302">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>615.8969959031837</v>
+        <v>407.1102990416741</v>
       </c>
     </row>
     <row r="303">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>616.3496102117134</v>
+        <v>295.353133364184</v>
       </c>
     </row>
     <row r="304">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>618.4095869413236</v>
+        <v>302.21659388239</v>
       </c>
     </row>
     <row r="305">
@@ -4998,11 +4998,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>616.0961971153129</v>
+        <v>299.2683693566714</v>
       </c>
     </row>
     <row r="306">
@@ -5013,11 +5013,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>200.2053993384051</v>
+        <v>265.2849324520069</v>
       </c>
     </row>
     <row r="307">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>271.365017209034</v>
+        <v>234.1539906552349</v>
       </c>
     </row>
     <row r="308">
@@ -5043,11 +5043,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>62.69887471408907</v>
+        <v>137.9645027339064</v>
       </c>
     </row>
     <row r="309">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>573.8387765074733</v>
+        <v>213.5800407661942</v>
       </c>
     </row>
     <row r="310">
@@ -5073,11 +5073,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>485.7432394022453</v>
+        <v>505.864554707247</v>
       </c>
     </row>
     <row r="311">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>66.0268932691002</v>
+        <v>140.4766831106095</v>
       </c>
     </row>
     <row r="312">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>198.7592680572442</v>
+        <v>263.2808293594302</v>
       </c>
     </row>
     <row r="313">
@@ -5118,11 +5118,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>63.30485937058388</v>
+        <v>146.8970220930177</v>
       </c>
     </row>
     <row r="314">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>171.2780401337388</v>
+        <v>252.0220765832538</v>
       </c>
     </row>
     <row r="315">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>207.2118431361766</v>
+        <v>290.8446586327354</v>
       </c>
     </row>
     <row r="316">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>596.9053902497836</v>
+        <v>419.8748338969282</v>
       </c>
     </row>
     <row r="317">
@@ -5178,11 +5178,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>121.7310041555266</v>
+        <v>202.3745627430987</v>
       </c>
     </row>
     <row r="318">
@@ -5193,11 +5193,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>49.89652576347511</v>
+        <v>131.3767754580934</v>
       </c>
     </row>
     <row r="319">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>617.4279070361644</v>
+        <v>405.4616480532131</v>
       </c>
     </row>
     <row r="320">
@@ -5223,11 +5223,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>575.0112439592498</v>
+        <v>257.7202175042919</v>
       </c>
     </row>
     <row r="321">
@@ -5238,11 +5238,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>619.2269057530879</v>
+        <v>299.2069770829289</v>
       </c>
     </row>
     <row r="322">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>167.0822270632482</v>
+        <v>225.2118983559744</v>
       </c>
     </row>
     <row r="323">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>270.1330052516413</v>
+        <v>233.1156151535796</v>
       </c>
     </row>
     <row r="324">
@@ -5283,11 +5283,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>123.9640433675536</v>
+        <v>174.6437031880509</v>
       </c>
     </row>
     <row r="325">
@@ -5298,11 +5298,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>185.6342827243591</v>
+        <v>258.0969226234916</v>
       </c>
     </row>
     <row r="326">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>59.72511885034409</v>
+        <v>143.4559287228808</v>
       </c>
     </row>
     <row r="327">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>614.1876446764838</v>
+        <v>298.5405184854939</v>
       </c>
     </row>
     <row r="328">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>607.6027114558465</v>
+        <v>291.9125166681933</v>
       </c>
     </row>
     <row r="329">
@@ -5358,11 +5358,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>241.5798000792561</v>
+        <v>201.6634020843782</v>
       </c>
     </row>
     <row r="330">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>218.3636872097339</v>
+        <v>187.3472114739193</v>
       </c>
     </row>
     <row r="331">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>626.661873619375</v>
+        <v>306.1498650987936</v>
       </c>
     </row>
     <row r="332">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>533.6077234554629</v>
+        <v>240.6553957539271</v>
       </c>
     </row>
     <row r="333">
@@ -5418,11 +5418,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>623.878251310231</v>
+        <v>305.5297858281983</v>
       </c>
     </row>
     <row r="334">
@@ -5433,11 +5433,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>201.3426454253737</v>
+        <v>265.5314730786209</v>
       </c>
     </row>
     <row r="335">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>103.1380002652348</v>
+        <v>115.8620035916273</v>
       </c>
     </row>
     <row r="336">
@@ -5463,11 +5463,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>256.7168714137835</v>
+        <v>325.2162572181462</v>
       </c>
     </row>
     <row r="337">
@@ -5478,11 +5478,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>95.76639060961472</v>
+        <v>176.0201727541978</v>
       </c>
     </row>
     <row r="338">
@@ -5493,11 +5493,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>260.3496983421461</v>
+        <v>242.8334230268776</v>
       </c>
     </row>
     <row r="339">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>339.5078169732922</v>
+        <v>262.5364558361898</v>
       </c>
     </row>
     <row r="340">
@@ -5523,11 +5523,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>268.4852574352886</v>
+        <v>244.4815171214456</v>
       </c>
     </row>
     <row r="341">
@@ -5538,11 +5538,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>246.0994041861252</v>
+        <v>249.0720943022942</v>
       </c>
     </row>
     <row r="342">
@@ -5553,11 +5553,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>244.0803400677385</v>
+        <v>130.0982456924606</v>
       </c>
     </row>
     <row r="343">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>265.1235430500931</v>
+        <v>244.7649577139401</v>
       </c>
     </row>
     <row r="344">
@@ -5583,11 +5583,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>220.5164664270967</v>
+        <v>170.4849151475579</v>
       </c>
     </row>
     <row r="345">
@@ -5598,11 +5598,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>266.4253604948988</v>
+        <v>247.3589627515343</v>
       </c>
     </row>
     <row r="346">
@@ -5613,11 +5613,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>262.1499381849978</v>
+        <v>250.7518419947306</v>
       </c>
     </row>
     <row r="347">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>256.6376844413774</v>
+        <v>245.2020554131428</v>
       </c>
     </row>
     <row r="348">
@@ -5643,11 +5643,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>272.121281660024</v>
+        <v>247.1939855447183</v>
       </c>
     </row>
     <row r="349">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>123.9955394119936</v>
+        <v>248.9481718440073</v>
       </c>
     </row>
     <row r="350">
@@ -5673,11 +5673,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>338.753579945603</v>
+        <v>262.8258537407512</v>
       </c>
     </row>
     <row r="351">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>244.9481478563077</v>
+        <v>243.9905079930992</v>
       </c>
     </row>
     <row r="352">
@@ -5703,11 +5703,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>128.1288650973908</v>
+        <v>245.7263957483557</v>
       </c>
     </row>
     <row r="353">
@@ -5718,11 +5718,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>270.1477232966168</v>
+        <v>241.3758450983825</v>
       </c>
     </row>
     <row r="354">
@@ -5733,11 +5733,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>224.5097660238579</v>
+        <v>173.6480917764453</v>
       </c>
     </row>
     <row r="355">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>319.9119139195989</v>
+        <v>255.3696671481475</v>
       </c>
     </row>
     <row r="356">
@@ -5763,11 +5763,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>127.30602726443</v>
+        <v>245.2199955591135</v>
       </c>
     </row>
     <row r="357">
@@ -5778,11 +5778,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>247.0030921458697</v>
+        <v>127.1680167975757</v>
       </c>
     </row>
     <row r="358">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>245.8723846358603</v>
+        <v>251.8859543154234</v>
       </c>
     </row>
     <row r="359">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>259.1175712553428</v>
+        <v>244.6616573423616</v>
       </c>
     </row>
     <row r="360">
@@ -5823,11 +5823,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>267.5215536520797</v>
+        <v>242.2130875979642</v>
       </c>
     </row>
     <row r="361">
@@ -5838,11 +5838,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>394.2085802884727</v>
+        <v>184.1323231692768</v>
       </c>
     </row>
     <row r="362">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>269.2177499230888</v>
+        <v>247.2555998483565</v>
       </c>
     </row>
     <row r="363">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>265.7120377715198</v>
+        <v>248.2500861193687</v>
       </c>
     </row>
     <row r="364">
@@ -5883,11 +5883,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>272.0407614309759</v>
+        <v>238.6138624870473</v>
       </c>
     </row>
     <row r="365">
@@ -5898,11 +5898,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>267.1609274923284</v>
+        <v>248.2464578486703</v>
       </c>
     </row>
     <row r="366">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>119.9739091585612</v>
+        <v>251.572927532271</v>
       </c>
     </row>
     <row r="367">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>393.9184922121719</v>
+        <v>230.4299203347763</v>
       </c>
     </row>
     <row r="368">
@@ -5943,11 +5943,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>283.3056721743233</v>
+        <v>230.0711370582394</v>
       </c>
     </row>
     <row r="369">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>755.4364692614545</v>
+        <v>66.73815255783093</v>
       </c>
     </row>
     <row r="370">
@@ -5973,11 +5973,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>737.0602738658094</v>
+        <v>34.52345300414044</v>
       </c>
     </row>
     <row r="371">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>407.9443120675884</v>
+        <v>317.946630304663</v>
       </c>
     </row>
     <row r="372">
@@ -6003,11 +6003,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>879.9928298660333</v>
+        <v>176.6888667503275</v>
       </c>
     </row>
     <row r="373">
@@ -6018,11 +6018,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>762.9026211265187</v>
+        <v>63.09525674037218</v>
       </c>
     </row>
     <row r="374">
@@ -6033,11 +6033,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>767.4385075145673</v>
+        <v>67.88592045568444</v>
       </c>
     </row>
     <row r="375">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>737.3593294495913</v>
+        <v>34.2181840897848</v>
       </c>
     </row>
     <row r="376">
@@ -6063,11 +6063,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>732.0924029321508</v>
+        <v>32.70858238462002</v>
       </c>
     </row>
     <row r="377">
@@ -6078,11 +6078,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>885.0784624488344</v>
+        <v>181.5158062914187</v>
       </c>
     </row>
     <row r="378">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>883.3096566025587</v>
+        <v>180.1765995943753</v>
       </c>
     </row>
     <row r="379">
@@ -6108,11 +6108,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>736.889207163484</v>
+        <v>35.38984638379532</v>
       </c>
     </row>
     <row r="380">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>844.8787435615096</v>
+        <v>148.9146243709701</v>
       </c>
     </row>
     <row r="381">
@@ -6138,11 +6138,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>455.5450121192576</v>
+        <v>292.1082656735446</v>
       </c>
     </row>
     <row r="382">
@@ -6153,11 +6153,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>734.8010227130336</v>
+        <v>33.3796757686011</v>
       </c>
     </row>
     <row r="383">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>732.5636727352477</v>
+        <v>31.90591786876936</v>
       </c>
     </row>
     <row r="384">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>735.2834981467736</v>
+        <v>33.24458419572206</v>
       </c>
     </row>
     <row r="385">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>763.5216114415061</v>
+        <v>63.43243743125071</v>
       </c>
     </row>
     <row r="386">
@@ -6213,11 +6213,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>453.3744570574661</v>
+        <v>293.4508617519292</v>
       </c>
     </row>
     <row r="387">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>739.4024454744151</v>
+        <v>37.08142664821583</v>
       </c>
     </row>
     <row r="388">
@@ -6243,11 +6243,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>728.3554642433388</v>
+        <v>29.33806901372546</v>
       </c>
     </row>
     <row r="389">
@@ -6258,11 +6258,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>728.7075752636654</v>
+        <v>28.37001636872408</v>
       </c>
     </row>
     <row r="390">
@@ -6273,11 +6273,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>738.2112070147015</v>
+        <v>39.11561759641163</v>
       </c>
     </row>
     <row r="391">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>909.2151633942545</v>
+        <v>203.8019484784353</v>
       </c>
     </row>
     <row r="392">
@@ -6303,11 +6303,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>730.4862665823251</v>
+        <v>31.02089893886271</v>
       </c>
     </row>
     <row r="393">
@@ -6318,11 +6318,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>887.7534123901355</v>
+        <v>184.6131265113243</v>
       </c>
     </row>
     <row r="394">
@@ -6333,11 +6333,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>725.6101542216179</v>
+        <v>27.58568935880062</v>
       </c>
     </row>
     <row r="395">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>715.8419916078705</v>
+        <v>30.56895919515435</v>
       </c>
     </row>
     <row r="396">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>707.3848536348678</v>
+        <v>599.7685658275938</v>
       </c>
     </row>
     <row r="397">
@@ -6378,11 +6378,11 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>402.8528284779557</v>
+        <v>418.910619457074</v>
       </c>
     </row>
     <row r="398">
@@ -6393,11 +6393,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>318.7461283580383</v>
+        <v>395.1452104601061</v>
       </c>
     </row>
     <row r="399">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>660.8614547036476</v>
+        <v>580.0655393103883</v>
       </c>
     </row>
     <row r="400">
@@ -6423,11 +6423,11 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>415.0220367356314</v>
+        <v>419.2014824656533</v>
       </c>
     </row>
     <row r="401">
@@ -6438,11 +6438,11 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>404.0941521558714</v>
+        <v>417.7719448167981</v>
       </c>
     </row>
     <row r="402">
@@ -6453,11 +6453,11 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>531.9172069611084</v>
+        <v>290.1088194372147</v>
       </c>
     </row>
     <row r="403">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>408.0188493815209</v>
+        <v>413.7000010176697</v>
       </c>
     </row>
     <row r="404">
@@ -6483,11 +6483,11 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>539.6096633611475</v>
+        <v>286.2644628689006</v>
       </c>
     </row>
     <row r="405">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>703.1264574838835</v>
+        <v>596.4055858326795</v>
       </c>
     </row>
     <row r="406">
@@ -6513,11 +6513,11 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>799.0464878757987</v>
+        <v>667.4815881169878</v>
       </c>
     </row>
     <row r="407">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>403.6412926718086</v>
+        <v>418.0305093436396</v>
       </c>
     </row>
     <row r="408">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>658.928053837548</v>
+        <v>577.1715434059126</v>
       </c>
     </row>
     <row r="409">
@@ -6558,11 +6558,11 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>531.1964786528766</v>
+        <v>291.0608337402675</v>
       </c>
     </row>
     <row r="410">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>702.5680044936581</v>
+        <v>596.9387958350218</v>
       </c>
     </row>
     <row r="411">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>404.3147527355172</v>
+        <v>417.601541343521</v>
       </c>
     </row>
     <row r="412">
@@ -6603,11 +6603,11 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>731.1957182903645</v>
+        <v>592.2228066044695</v>
       </c>
     </row>
     <row r="413">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>513.4781853654288</v>
+        <v>316.9706336802632</v>
       </c>
     </row>
     <row r="414">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>691.0893860919261</v>
+        <v>623.8236912874983</v>
       </c>
     </row>
     <row r="415">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>689.0716245778688</v>
+        <v>631.3880668617128</v>
       </c>
     </row>
     <row r="416">
@@ -6663,11 +6663,11 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>733.8647042878714</v>
+        <v>594.4100784430385</v>
       </c>
     </row>
     <row r="417">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>687.9706222615004</v>
+        <v>620.2615824043411</v>
       </c>
     </row>
     <row r="418">
@@ -6693,11 +6693,11 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>471.9688111199325</v>
+        <v>204.5305974443592</v>
       </c>
     </row>
     <row r="419">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>392.8925776521635</v>
+        <v>110.2827409697895</v>
       </c>
     </row>
     <row r="420">
@@ -6723,11 +6723,11 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>468.1659299344697</v>
+        <v>204.4596365169506</v>
       </c>
     </row>
     <row r="421">
@@ -6738,11 +6738,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>437.6301333322829</v>
+        <v>163.7742200848483</v>
       </c>
     </row>
     <row r="422">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>469.3464139810218</v>
+        <v>208.7913962749197</v>
       </c>
     </row>
     <row r="423">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>404.1736028081135</v>
+        <v>121.5759418094487</v>
       </c>
     </row>
     <row r="424">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>475.7548095131403</v>
+        <v>213.2182452585202</v>
       </c>
     </row>
     <row r="425">
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>374.4568889247058</v>
+        <v>176.2503739454197</v>
       </c>
     </row>
     <row r="426">
@@ -6813,11 +6813,11 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>398.5444258603678</v>
+        <v>231.1188408667959</v>
       </c>
     </row>
     <row r="427">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>477.6547662961582</v>
+        <v>213.4509778017186</v>
       </c>
     </row>
     <row r="428">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>372.3583100653588</v>
+        <v>181.948223952247</v>
       </c>
     </row>
     <row r="429">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>376.8661815300433</v>
+        <v>94.86397367730432</v>
       </c>
     </row>
     <row r="430">
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>382.8441201566035</v>
+        <v>100.5714524373624</v>
       </c>
     </row>
     <row r="431">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>330.9711404490843</v>
+        <v>48.39588948557887</v>
       </c>
     </row>
     <row r="432">
@@ -6903,11 +6903,11 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>396.4694872636811</v>
+        <v>463.4459507527332</v>
       </c>
     </row>
     <row r="433">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>548.1075770880702</v>
+        <v>433.5621327582323</v>
       </c>
     </row>
     <row r="434">
@@ -6933,11 +6933,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>338.3448745348402</v>
+        <v>229.0852832585927</v>
       </c>
     </row>
     <row r="435">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>364.9139797676369</v>
+        <v>172.6159711788848</v>
       </c>
     </row>
     <row r="436">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>400.3918586212197</v>
+        <v>117.7951780549381</v>
       </c>
     </row>
     <row r="437">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>379.8599159448746</v>
+        <v>97.45745982829436</v>
       </c>
     </row>
     <row r="438">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>383.8761460419659</v>
+        <v>101.481381795035</v>
       </c>
     </row>
     <row r="439">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>523.1538446003622</v>
+        <v>510.997654198796</v>
       </c>
     </row>
     <row r="440">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>540.4447070157765</v>
+        <v>429.4902768901852</v>
       </c>
     </row>
     <row r="441">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>541.063100766626</v>
+        <v>260.2853585002077</v>
       </c>
     </row>
     <row r="442">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>361.7951034920814</v>
+        <v>208.5962880424154</v>
       </c>
     </row>
     <row r="443">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>379.865662713909</v>
+        <v>98.25808763279977</v>
       </c>
     </row>
     <row r="444">
@@ -7083,11 +7083,11 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>472.3741090501651</v>
+        <v>208.4277253435319</v>
       </c>
     </row>
     <row r="445">
@@ -7098,11 +7098,11 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>478.0656556116565</v>
+        <v>212.3386261781216</v>
       </c>
     </row>
     <row r="446">
@@ -7113,11 +7113,11 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>470.8794772176558</v>
+        <v>209.6504118209775</v>
       </c>
     </row>
     <row r="447">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>376.3643359901362</v>
+        <v>182.7667459903581</v>
       </c>
     </row>
     <row r="448">
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>539.3000932963816</v>
+        <v>423.5769488863627</v>
       </c>
     </row>
     <row r="449">
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>377.8027639282422</v>
+        <v>95.67790461919937</v>
       </c>
     </row>
     <row r="450">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>423.1133016556792</v>
+        <v>484.1532863787845</v>
       </c>
     </row>
     <row r="451">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>398.4308918550063</v>
+        <v>228.5218675824255</v>
       </c>
     </row>
     <row r="452">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>384.5226986211789</v>
+        <v>102.6353178628117</v>
       </c>
     </row>
     <row r="453">
@@ -7218,11 +7218,11 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>289.6683614717405</v>
+        <v>301.0507133735346</v>
       </c>
     </row>
     <row r="454">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>476.671625154577</v>
+        <v>386.2146034980639</v>
       </c>
     </row>
     <row r="455">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>379.2930854802572</v>
+        <v>97.23843853479993</v>
       </c>
     </row>
     <row r="456">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>384.8164371505356</v>
+        <v>102.4918480857375</v>
       </c>
     </row>
     <row r="457">
@@ -7278,11 +7278,11 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>471.1318091223583</v>
+        <v>207.4009137645875</v>
       </c>
     </row>
     <row r="458">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>544.1825747253724</v>
+        <v>428.9279411296831</v>
       </c>
     </row>
     <row r="459">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>399.465320450838</v>
+        <v>229.5591365467445</v>
       </c>
     </row>
     <row r="460">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>369.0119065625322</v>
+        <v>175.6247251323167</v>
       </c>
     </row>
     <row r="461">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>370.650238082961</v>
+        <v>175.3296764752763</v>
       </c>
     </row>
     <row r="462">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>333.6557619236073</v>
+        <v>51.09998502013926</v>
       </c>
     </row>
     <row r="463">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>382.0640370627376</v>
+        <v>99.97599824829125</v>
       </c>
     </row>
     <row r="464">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>362.2230741759088</v>
+        <v>168.7811319371953</v>
       </c>
     </row>
     <row r="465">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>474.2378592001739</v>
+        <v>211.6732813870892</v>
       </c>
     </row>
     <row r="466">
@@ -7413,11 +7413,11 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>401.665465879754</v>
+        <v>232.6220725104062</v>
       </c>
     </row>
     <row r="467">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>382.3170143239886</v>
+        <v>100.092607826785</v>
       </c>
     </row>
     <row r="468">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>379.0448476203267</v>
+        <v>96.94585824993405</v>
       </c>
     </row>
     <row r="469">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>374.9042615607714</v>
+        <v>178.0547726996159</v>
       </c>
     </row>
     <row r="470">
@@ -7473,11 +7473,11 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>473.324159641636</v>
+        <v>209.6007710482695</v>
       </c>
     </row>
     <row r="471">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>480.2135545670378</v>
+        <v>217.769738655443</v>
       </c>
     </row>
     <row r="472">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>385.2222955395411</v>
+        <v>102.700602997662</v>
       </c>
     </row>
     <row r="473">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>367.3860009118215</v>
+        <v>172.7706883374275</v>
       </c>
     </row>
     <row r="474">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>542.1827885381606</v>
+        <v>429.3340900803877</v>
       </c>
     </row>
     <row r="475">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>381.8848835748896</v>
+        <v>99.365783649566</v>
       </c>
     </row>
     <row r="476">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>538.5790438625913</v>
+        <v>426.3835440125061</v>
       </c>
     </row>
     <row r="477">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>368.6459573800726</v>
+        <v>178.0194198959729</v>
       </c>
     </row>
     <row r="478">
@@ -7593,11 +7593,11 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>474.7514143995931</v>
+        <v>208.9435669676058</v>
       </c>
     </row>
     <row r="479">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>373.9469958264402</v>
+        <v>178.8457234807114</v>
       </c>
     </row>
     <row r="480">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>389.8667975757295</v>
+        <v>107.3145602966586</v>
       </c>
     </row>
     <row r="481">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>356.9198182307821</v>
+        <v>78.34448568653632</v>
       </c>
     </row>
     <row r="482">
@@ -7653,11 +7653,11 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>538.4207338192327</v>
+        <v>494.2465546328309</v>
       </c>
     </row>
     <row r="483">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>486.8211826868632</v>
+        <v>208.6719006944995</v>
       </c>
     </row>
     <row r="484">
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>361.6643405946432</v>
+        <v>173.0380180324195</v>
       </c>
     </row>
     <row r="485">
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>401.930851393678</v>
+        <v>306.8243085037814</v>
       </c>
     </row>
     <row r="486">
@@ -7713,11 +7713,11 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>519.2538226536985</v>
+        <v>509.5008732297528</v>
       </c>
     </row>
     <row r="487">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>279.902734174244</v>
+        <v>163.7335498059527</v>
       </c>
     </row>
     <row r="488">
@@ -7743,11 +7743,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>421.8829865894261</v>
+        <v>482.7255904190506</v>
       </c>
     </row>
     <row r="489">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>369.4452532027314</v>
+        <v>176.3452400412433</v>
       </c>
     </row>
     <row r="490">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>378.3849475489089</v>
+        <v>96.72437721924653</v>
       </c>
     </row>
     <row r="491">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>421.4524250593868</v>
+        <v>482.017426840228</v>
       </c>
     </row>
     <row r="492">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>495.327109267422</v>
+        <v>228.9300086027407</v>
       </c>
     </row>
     <row r="493">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>357.2115310266433</v>
+        <v>144.5352295904483</v>
       </c>
     </row>
     <row r="494">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>399.4831107472828</v>
+        <v>304.1258562519051</v>
       </c>
     </row>
     <row r="495">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>370.8772421201244</v>
+        <v>176.328593549544</v>
       </c>
     </row>
     <row r="496">
@@ -7863,11 +7863,11 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>496.2179314352944</v>
+        <v>345.6396454305997</v>
       </c>
     </row>
     <row r="497">
@@ -7878,11 +7878,11 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>508.6165235388352</v>
+        <v>204.2468831622038</v>
       </c>
     </row>
     <row r="498">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>320.0585897987742</v>
+        <v>78.46596702303529</v>
       </c>
     </row>
     <row r="499">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>301.6603319138252</v>
+        <v>38.42670238202552</v>
       </c>
     </row>
     <row r="500">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>399.3228032090287</v>
+        <v>228.1579527766796</v>
       </c>
     </row>
     <row r="501">
@@ -7938,11 +7938,11 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>396.5711271812636</v>
+        <v>229.1174983035737</v>
       </c>
     </row>
     <row r="502">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>403.9857614874821</v>
+        <v>121.9724126682299</v>
       </c>
     </row>
     <row r="503">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>399.6670938287053</v>
+        <v>229.178044449383</v>
       </c>
     </row>
     <row r="504">
@@ -7983,11 +7983,11 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>429.5073032500679</v>
+        <v>216.9896041973278</v>
       </c>
     </row>
     <row r="505">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>394.7884522559071</v>
+        <v>112.4827109906133</v>
       </c>
     </row>
   </sheetData>

--- a/store_dc_distances.xlsx
+++ b/store_dc_distances.xlsx
@@ -453,11 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.8460057247369</v>
+        <v>330.9635282855404</v>
       </c>
     </row>
     <row r="3">
@@ -468,11 +468,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.4928162679067</v>
+        <v>117.9924090723754</v>
       </c>
     </row>
     <row r="4">
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>365.5697738719786</v>
+        <v>426.9669887847988</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>137.1836921009171</v>
+        <v>121.6518811104223</v>
       </c>
     </row>
     <row r="6">
@@ -513,11 +513,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>370.9274282971861</v>
+        <v>420.4712712853633</v>
       </c>
     </row>
     <row r="7">
@@ -528,11 +528,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135.1668889158399</v>
+        <v>108.1103102442499</v>
       </c>
     </row>
     <row r="8">
@@ -543,11 +543,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>245.074598671275</v>
+        <v>236.9722186769305</v>
       </c>
     </row>
     <row r="9">
@@ -558,11 +558,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>304.8226550499002</v>
+        <v>295.3716828864031</v>
       </c>
     </row>
     <row r="10">
@@ -573,11 +573,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>466.4283882980909</v>
+        <v>495.1232190037021</v>
       </c>
     </row>
     <row r="11">
@@ -588,11 +588,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>472.7473727202855</v>
+        <v>492.2082518359087</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>151.0314023786419</v>
+        <v>128.9441347688719</v>
       </c>
     </row>
     <row r="13">
@@ -618,11 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>155.8689391528941</v>
+        <v>130.2855787087994</v>
       </c>
     </row>
     <row r="14">
@@ -633,11 +633,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170.9279161682704</v>
+        <v>146.4901253335264</v>
       </c>
     </row>
     <row r="15">
@@ -648,11 +648,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>413.5495142717604</v>
+        <v>453.1047927312811</v>
       </c>
     </row>
     <row r="16">
@@ -663,11 +663,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>414.1680610379193</v>
+        <v>401.849670130051</v>
       </c>
     </row>
     <row r="17">
@@ -678,11 +678,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>155.8711978103603</v>
+        <v>128.5054911990155</v>
       </c>
     </row>
     <row r="18">
@@ -693,11 +693,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>197.3786891663952</v>
+        <v>179.8330479062113</v>
       </c>
     </row>
     <row r="19">
@@ -708,11 +708,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150.8606934652393</v>
+        <v>130.5207868271966</v>
       </c>
     </row>
     <row r="20">
@@ -723,11 +723,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>147.942072551742</v>
+        <v>170.3468154702016</v>
       </c>
     </row>
     <row r="21">
@@ -738,11 +738,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>170.0748304559448</v>
+        <v>147.6369671603444</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>274.7525032714101</v>
+        <v>276.1174878980499</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>422.7970840515572</v>
+        <v>465.5664978287974</v>
       </c>
     </row>
     <row r="24">
@@ -783,11 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44.80763566563145</v>
+        <v>20.47034300213973</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>392.7470920930622</v>
+        <v>440.6263987667413</v>
       </c>
     </row>
     <row r="26">
@@ -813,11 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>296.4696464613529</v>
+        <v>287.0633257945925</v>
       </c>
     </row>
     <row r="27">
@@ -828,11 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>162.1806222902383</v>
+        <v>137.5875559259532</v>
       </c>
     </row>
     <row r="28">
@@ -843,11 +843,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>390.3002980085579</v>
+        <v>437.5011742973805</v>
       </c>
     </row>
     <row r="29">
@@ -858,11 +858,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>106.6790260503075</v>
+        <v>86.28571933028022</v>
       </c>
     </row>
     <row r="30">
@@ -873,11 +873,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>260.1363480138145</v>
+        <v>285.2711516650368</v>
       </c>
     </row>
     <row r="31">
@@ -888,11 +888,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>156.190021202696</v>
+        <v>137.8003887622026</v>
       </c>
     </row>
     <row r="32">
@@ -903,11 +903,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160.9219624355327</v>
+        <v>139.3399391111659</v>
       </c>
     </row>
     <row r="33">
@@ -918,11 +918,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>398.7773663232627</v>
+        <v>446.4715004339711</v>
       </c>
     </row>
     <row r="34">
@@ -933,11 +933,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>159.2187052602542</v>
+        <v>137.0910817780116</v>
       </c>
     </row>
     <row r="35">
@@ -948,11 +948,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>159.2061091161018</v>
+        <v>137.1927821035483</v>
       </c>
     </row>
     <row r="36">
@@ -963,11 +963,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>467.3803848016624</v>
+        <v>495.716185770717</v>
       </c>
     </row>
     <row r="37">
@@ -978,11 +978,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>44.22068792538425</v>
+        <v>20.19869826917071</v>
       </c>
     </row>
     <row r="38">
@@ -993,11 +993,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>155.3531487189899</v>
+        <v>132.5567661736015</v>
       </c>
     </row>
     <row r="39">
@@ -1008,11 +1008,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>384.5306082334927</v>
+        <v>432.38924585193</v>
       </c>
     </row>
     <row r="40">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>284.4129910582891</v>
+        <v>275.726143177566</v>
       </c>
     </row>
     <row r="41">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.49259868729828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>230.7789116574628</v>
+        <v>265.3216686549943</v>
       </c>
     </row>
     <row r="43">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>94.04767826631056</v>
+        <v>113.2095459182907</v>
       </c>
     </row>
     <row r="44">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>382.7309042653473</v>
+        <v>444.1175443051316</v>
       </c>
     </row>
     <row r="45">
@@ -1098,11 +1098,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>277.0434321345084</v>
+        <v>266.6468275894603</v>
       </c>
     </row>
     <row r="46">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>363.3676583725137</v>
+        <v>407.277294246931</v>
       </c>
     </row>
     <row r="47">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>367.859288993661</v>
+        <v>413.8102117955148</v>
       </c>
     </row>
     <row r="48">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>148.5993207899491</v>
+        <v>122.8011678761479</v>
       </c>
     </row>
     <row r="49">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>394.3261874511825</v>
+        <v>442.4265618572776</v>
       </c>
     </row>
     <row r="50">
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>466.862664902199</v>
+        <v>494.2392037869573</v>
       </c>
     </row>
     <row r="51">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>244.0476712680346</v>
+        <v>235.567208404973</v>
       </c>
     </row>
     <row r="52">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>105.0335556921193</v>
+        <v>127.9311147058719</v>
       </c>
     </row>
     <row r="53">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>109.7389620112709</v>
+        <v>85.96947799636601</v>
       </c>
     </row>
     <row r="54">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>108.6104453741741</v>
+        <v>118.4108809723095</v>
       </c>
     </row>
     <row r="55">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>164.3915028407905</v>
+        <v>141.7811728221151</v>
       </c>
     </row>
     <row r="56">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>462.2694883273145</v>
+        <v>490.0243432034919</v>
       </c>
     </row>
     <row r="57">
@@ -1278,11 +1278,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>378.9423803573275</v>
+        <v>392.1441159670266</v>
       </c>
     </row>
     <row r="58">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>100.7259767775823</v>
+        <v>124.8455044460658</v>
       </c>
     </row>
     <row r="59">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>165.351606625248</v>
+        <v>145.9883362263176</v>
       </c>
     </row>
     <row r="60">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>155.0573123555761</v>
+        <v>133.1781377095647</v>
       </c>
     </row>
     <row r="61">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>109.6785426341018</v>
+        <v>132.4012953218188</v>
       </c>
     </row>
     <row r="62">
@@ -1353,11 +1353,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>146.6430460690046</v>
+        <v>123.0549928591128</v>
       </c>
     </row>
     <row r="63">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>393.1682837749015</v>
+        <v>440.5761630353377</v>
       </c>
     </row>
     <row r="64">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>245.079558964301</v>
+        <v>237.0082605430272</v>
       </c>
     </row>
     <row r="65">
@@ -1398,11 +1398,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>92.73717022738394</v>
+        <v>112.1216799225184</v>
       </c>
     </row>
     <row r="66">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>299.3569840336716</v>
+        <v>290.2997824974207</v>
       </c>
     </row>
     <row r="67">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>144.2270060908566</v>
+        <v>120.0711060212944</v>
       </c>
     </row>
     <row r="68">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>103.496349890505</v>
+        <v>95.52643598416643</v>
       </c>
     </row>
     <row r="69">
@@ -1458,11 +1458,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68.27692687408248</v>
+        <v>20.41596783227257</v>
       </c>
     </row>
     <row r="70">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>160.2128384245894</v>
+        <v>134.7397854755224</v>
       </c>
     </row>
     <row r="71">
@@ -1488,11 +1488,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100.7259767775823</v>
+        <v>124.8455044460658</v>
       </c>
     </row>
     <row r="72">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>153.1285040266745</v>
+        <v>126.3772556143692</v>
       </c>
     </row>
     <row r="73">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>409.2001225630211</v>
+        <v>449.7586404666938</v>
       </c>
     </row>
     <row r="74">
@@ -1533,11 +1533,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>151.6020550227136</v>
+        <v>127.1359911457164</v>
       </c>
     </row>
     <row r="75">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>96.58126533093416</v>
+        <v>118.9906694931409</v>
       </c>
     </row>
     <row r="76">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>450.0229442223006</v>
+        <v>483.7945945807476</v>
       </c>
     </row>
     <row r="77">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>103.6119916373755</v>
+        <v>127.0006139161995</v>
       </c>
     </row>
     <row r="78">
@@ -1593,11 +1593,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>190.6825132721265</v>
+        <v>203.6346669013843</v>
       </c>
     </row>
     <row r="79">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>223.9844703950944</v>
+        <v>234.5085396974142</v>
       </c>
     </row>
     <row r="80">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>168.4133991841169</v>
+        <v>143.7534492312146</v>
       </c>
     </row>
     <row r="81">
@@ -1638,11 +1638,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>159.9084196272836</v>
+        <v>133.7006511831521</v>
       </c>
     </row>
     <row r="82">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>155.1193933778405</v>
+        <v>128.6823365844351</v>
       </c>
     </row>
     <row r="83">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>109.7499568719103</v>
+        <v>132.6130702067358</v>
       </c>
     </row>
     <row r="84">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>103.1628998334891</v>
+        <v>125.6521233991047</v>
       </c>
     </row>
     <row r="85">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>93.89827386045394</v>
+        <v>113.4975601647661</v>
       </c>
     </row>
     <row r="86">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>154.4089620521199</v>
+        <v>130.2231289710547</v>
       </c>
     </row>
     <row r="87">
@@ -1728,11 +1728,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>297.954671485222</v>
+        <v>288.7402552400748</v>
       </c>
     </row>
     <row r="88">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>244.9376359487637</v>
+        <v>236.5461713897413</v>
       </c>
     </row>
     <row r="89">
@@ -1758,11 +1758,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>158.5499688032886</v>
+        <v>135.6068269194521</v>
       </c>
     </row>
     <row r="90">
@@ -1773,11 +1773,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>158.4325457480821</v>
+        <v>133.4495554787986</v>
       </c>
     </row>
     <row r="91">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>150.0773248273609</v>
+        <v>124.0579963162462</v>
       </c>
     </row>
     <row r="92">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>111.1930211145544</v>
+        <v>134.3726052010849</v>
       </c>
     </row>
     <row r="93">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>103.1395370676297</v>
+        <v>125.8855478394724</v>
       </c>
     </row>
     <row r="94">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>157.2643207295644</v>
+        <v>131.7009008617561</v>
       </c>
     </row>
     <row r="95">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>110.9238212584267</v>
+        <v>133.9028375627812</v>
       </c>
     </row>
     <row r="96">
@@ -1863,11 +1863,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>154.3148811061609</v>
+        <v>133.3419133050184</v>
       </c>
     </row>
     <row r="97">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>160.7866229667267</v>
+        <v>136.3714144979849</v>
       </c>
     </row>
     <row r="98">
@@ -1893,11 +1893,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>153.2436065110408</v>
+        <v>130.4915498302243</v>
       </c>
     </row>
     <row r="99">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>394.5056466031788</v>
+        <v>442.2738823209808</v>
       </c>
     </row>
     <row r="100">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>163.2868500698719</v>
+        <v>139.9394903277591</v>
       </c>
     </row>
     <row r="101">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>150.4724269081669</v>
+        <v>128.2753586164148</v>
       </c>
     </row>
     <row r="102">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>140.3539978684227</v>
+        <v>116.0060286591594</v>
       </c>
     </row>
     <row r="103">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>147.6036965257908</v>
+        <v>119.7946518548475</v>
       </c>
     </row>
     <row r="104">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>140.9713963838633</v>
+        <v>117.7208691827655</v>
       </c>
     </row>
     <row r="105">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>382.5222745361521</v>
+        <v>443.7056571528461</v>
       </c>
     </row>
     <row r="106">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>262.7324413613346</v>
+        <v>287.2407268146017</v>
       </c>
     </row>
     <row r="107">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>463.6203705187395</v>
+        <v>491.1606421189047</v>
       </c>
     </row>
     <row r="108">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>390.2487772391969</v>
+        <v>438.3360268021133</v>
       </c>
     </row>
     <row r="109">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>153.539195695105</v>
+        <v>128.4727129154797</v>
       </c>
     </row>
     <row r="110">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>297.4728206135632</v>
+        <v>288.3934749946374</v>
       </c>
     </row>
     <row r="111">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>157.7435654334739</v>
+        <v>131.4380690737538</v>
       </c>
     </row>
     <row r="112">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>146.3339933783038</v>
+        <v>121.1765276823574</v>
       </c>
     </row>
     <row r="113">
@@ -2118,11 +2118,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>149.9757318464934</v>
+        <v>121.6051186359468</v>
       </c>
     </row>
     <row r="114">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>275.4336495404298</v>
+        <v>315.3898871045468</v>
       </c>
     </row>
     <row r="115">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>367.0969959282192</v>
+        <v>420.9097798142605</v>
       </c>
     </row>
     <row r="116">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>143.5474732221657</v>
+        <v>117.1189359683959</v>
       </c>
     </row>
     <row r="117">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>106.0711509208065</v>
+        <v>128.1772702393585</v>
       </c>
     </row>
     <row r="118">
@@ -2193,11 +2193,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>158.0974000785128</v>
+        <v>134.3931990270278</v>
       </c>
     </row>
     <row r="119">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>463.8843261091552</v>
+        <v>491.9232670955004</v>
       </c>
     </row>
     <row r="120">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>297.8104472791561</v>
+        <v>288.7137580132629</v>
       </c>
     </row>
     <row r="121">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>162.1540802945918</v>
+        <v>139.8497216179582</v>
       </c>
     </row>
     <row r="122">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>150.4196753751032</v>
+        <v>127.549787869981</v>
       </c>
     </row>
     <row r="123">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>40.73116379217367</v>
+        <v>17.16754590109464</v>
       </c>
     </row>
     <row r="124">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>151.2941074551429</v>
+        <v>125.9160263320814</v>
       </c>
     </row>
     <row r="125">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>137.6423599800942</v>
+        <v>115.1672335283907</v>
       </c>
     </row>
     <row r="126">
@@ -2313,11 +2313,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>141.7442910967588</v>
+        <v>111.8178194902709</v>
       </c>
     </row>
     <row r="127">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>152.1140732346485</v>
+        <v>131.1888744670751</v>
       </c>
     </row>
     <row r="128">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>148.417679040193</v>
+        <v>123.935072258068</v>
       </c>
     </row>
     <row r="129">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>155.2912736366582</v>
+        <v>131.6487906909689</v>
       </c>
     </row>
     <row r="130">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>153.7467056988309</v>
+        <v>130.381237786289</v>
       </c>
     </row>
     <row r="131">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>68.55822665796128</v>
+        <v>2.524349787145492</v>
       </c>
     </row>
     <row r="132">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>47.08708195175153</v>
+        <v>69.52376245901762</v>
       </c>
     </row>
     <row r="133">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>391.8184530774033</v>
+        <v>439.4150303327746</v>
       </c>
     </row>
     <row r="134">
@@ -2433,11 +2433,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>157.8095881689238</v>
+        <v>132.7490468314282</v>
       </c>
     </row>
     <row r="135">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>171.5590778179512</v>
+        <v>149.1626153246674</v>
       </c>
     </row>
     <row r="136">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>102.338791598857</v>
+        <v>123.6480037344783</v>
       </c>
     </row>
     <row r="137">
@@ -2478,11 +2478,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>105.4461159483704</v>
+        <v>126.8999961435841</v>
       </c>
     </row>
     <row r="138">
@@ -2493,11 +2493,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>154.3020684321744</v>
+        <v>127.3032429697211</v>
       </c>
     </row>
     <row r="139">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>144.0207040191272</v>
+        <v>121.1956400146447</v>
       </c>
     </row>
     <row r="140">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>388.4867996322367</v>
+        <v>436.7912830403555</v>
       </c>
     </row>
     <row r="141">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>160.4530529800002</v>
+        <v>135.4344329345909</v>
       </c>
     </row>
     <row r="142">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>279.7075176862222</v>
+        <v>280.444170825078</v>
       </c>
     </row>
     <row r="143">
@@ -2568,11 +2568,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>137.8802470023848</v>
+        <v>106.2678263285794</v>
       </c>
     </row>
     <row r="144">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>125.8355096270716</v>
+        <v>103.5750652214989</v>
       </c>
     </row>
     <row r="145">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>369.1622100435767</v>
+        <v>423.1317561742813</v>
       </c>
     </row>
     <row r="146">
@@ -2613,11 +2613,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>40.93402369732947</v>
+        <v>16.86922051279774</v>
       </c>
     </row>
     <row r="147">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>146.5562506993173</v>
+        <v>120.0628786795913</v>
       </c>
     </row>
     <row r="148">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>145.0353621763646</v>
+        <v>127.0843658238061</v>
       </c>
     </row>
     <row r="149">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>157.1304892525723</v>
+        <v>137.6740764380879</v>
       </c>
     </row>
     <row r="150">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>121.03539755116</v>
+        <v>98.92679672304133</v>
       </c>
     </row>
     <row r="151">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>378.6092271739076</v>
+        <v>427.5095658720282</v>
       </c>
     </row>
     <row r="152">
@@ -2703,11 +2703,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>453.0618631701936</v>
+        <v>487.5368227657868</v>
       </c>
     </row>
     <row r="153">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>150.9465552515387</v>
+        <v>123.5184011830669</v>
       </c>
     </row>
     <row r="154">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>26.39503825315914</v>
+        <v>2.195284483350534</v>
       </c>
     </row>
     <row r="155">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>139.6648102466222</v>
+        <v>115.0570084748459</v>
       </c>
     </row>
     <row r="156">
@@ -2763,11 +2763,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>147.6298806526679</v>
+        <v>126.05341869692</v>
       </c>
     </row>
     <row r="157">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>466.5173357135325</v>
+        <v>494.1176797046688</v>
       </c>
     </row>
     <row r="158">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>378.5505972995411</v>
+        <v>439.6105513810847</v>
       </c>
     </row>
     <row r="159">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>166.3585398305499</v>
+        <v>141.1308776121495</v>
       </c>
     </row>
     <row r="160">
@@ -2823,11 +2823,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>295.1284815246919</v>
+        <v>286.0952964076756</v>
       </c>
     </row>
     <row r="161">
@@ -2838,11 +2838,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>148.430521977768</v>
+        <v>128.2123748624244</v>
       </c>
     </row>
     <row r="162">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>160.9527014377235</v>
+        <v>137.7535479338831</v>
       </c>
     </row>
     <row r="163">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>66.16610374030769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>403.3770685462418</v>
+        <v>422.87760814889</v>
       </c>
     </row>
     <row r="165">
@@ -2898,11 +2898,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>369.9360371615572</v>
+        <v>424.1932020833065</v>
       </c>
     </row>
     <row r="166">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>312.3121417069709</v>
+        <v>366.8659341721198</v>
       </c>
     </row>
     <row r="167">
@@ -2928,11 +2928,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>157.9650373618147</v>
+        <v>136.6273011118156</v>
       </c>
     </row>
     <row r="168">
@@ -2943,11 +2943,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>97.45824180501572</v>
+        <v>116.8619030719691</v>
       </c>
     </row>
     <row r="169">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>43.97404253119719</v>
+        <v>67.14739972868296</v>
       </c>
     </row>
     <row r="170">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>140.7851946362896</v>
+        <v>110.0155394868578</v>
       </c>
     </row>
     <row r="171">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>399.5083708833428</v>
+        <v>441.4650566886497</v>
       </c>
     </row>
     <row r="172">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>161.5314469475466</v>
+        <v>135.8642245783005</v>
       </c>
     </row>
     <row r="173">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>152.6882497958964</v>
+        <v>135.5652887863286</v>
       </c>
     </row>
     <row r="174">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>130.9552456548431</v>
+        <v>108.3634492007963</v>
       </c>
     </row>
     <row r="175">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>110.1578374848856</v>
+        <v>133.6289924038313</v>
       </c>
     </row>
     <row r="176">
@@ -3063,11 +3063,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>198.8890780199291</v>
+        <v>181.4012272520388</v>
       </c>
     </row>
     <row r="177">
@@ -3078,11 +3078,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>266.3355288928579</v>
+        <v>291.7330142189344</v>
       </c>
     </row>
     <row r="178">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>387.6774496753766</v>
+        <v>436.0282594747227</v>
       </c>
     </row>
     <row r="179">
@@ -3108,11 +3108,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>143.8721470076325</v>
+        <v>116.4654686920483</v>
       </c>
     </row>
     <row r="180">
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>140.9664354752053</v>
+        <v>147.1133911629679</v>
       </c>
     </row>
     <row r="181">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>142.7213522013847</v>
+        <v>112.1407207819316</v>
       </c>
     </row>
     <row r="182">
@@ -3153,11 +3153,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>156.9633839319166</v>
+        <v>134.5946867737809</v>
       </c>
     </row>
     <row r="183">
@@ -3168,11 +3168,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>156.7968949445768</v>
+        <v>134.9979401079424</v>
       </c>
     </row>
     <row r="184">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>145.3817134522845</v>
+        <v>116.9610396796634</v>
       </c>
     </row>
     <row r="185">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>164.8960223765515</v>
+        <v>141.1914671328136</v>
       </c>
     </row>
     <row r="186">
@@ -3213,11 +3213,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>160.1367601744726</v>
+        <v>134.8274477844502</v>
       </c>
     </row>
     <row r="187">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>94.57825916665728</v>
+        <v>115.5589954023719</v>
       </c>
     </row>
     <row r="188">
@@ -3243,11 +3243,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>149.0413074483496</v>
+        <v>124.0243692895168</v>
       </c>
     </row>
     <row r="189">
@@ -3258,11 +3258,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>105.1204904123371</v>
+        <v>128.3784927693047</v>
       </c>
     </row>
     <row r="190">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>388.2139984601232</v>
+        <v>438.2231249765429</v>
       </c>
     </row>
     <row r="191">
@@ -3288,11 +3288,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>46.05181255247427</v>
+        <v>68.87078381624423</v>
       </c>
     </row>
     <row r="192">
@@ -3303,11 +3303,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>393.715675009759</v>
+        <v>436.3721841702692</v>
       </c>
     </row>
     <row r="193">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>365.5773635412867</v>
+        <v>418.9682152063426</v>
       </c>
     </row>
     <row r="194">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>90.42836908835832</v>
+        <v>66.87147235620471</v>
       </c>
     </row>
     <row r="195">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>132.9341213620754</v>
+        <v>111.7612942561259</v>
       </c>
     </row>
     <row r="196">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>148.6479009466308</v>
+        <v>134.711526205172</v>
       </c>
     </row>
     <row r="197">
@@ -3378,11 +3378,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>90.66046051512869</v>
+        <v>113.9739665090551</v>
       </c>
     </row>
     <row r="198">
@@ -3393,11 +3393,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>138.4670632375975</v>
+        <v>116.9153879128728</v>
       </c>
     </row>
     <row r="199">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>144.8737354091315</v>
+        <v>119.4607446504558</v>
       </c>
     </row>
     <row r="200">
@@ -3423,11 +3423,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>150.6046320137467</v>
+        <v>128.1223886851244</v>
       </c>
     </row>
     <row r="201">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>141.2826203035115</v>
+        <v>114.3936628670256</v>
       </c>
     </row>
     <row r="202">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>151.6595942303774</v>
+        <v>133.3570028934936</v>
       </c>
     </row>
     <row r="203">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>68.87397011120331</v>
+        <v>80.39050753268133</v>
       </c>
     </row>
     <row r="204">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>125.0677805919528</v>
+        <v>102.4988016091568</v>
       </c>
     </row>
     <row r="205">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>81.78595913441407</v>
+        <v>104.8494011357226</v>
       </c>
     </row>
     <row r="206">
@@ -3513,11 +3513,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>140.0590297326085</v>
+        <v>159.4643923886767</v>
       </c>
     </row>
     <row r="207">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>98.7323172694025</v>
+        <v>120.0040682159923</v>
       </c>
     </row>
     <row r="208">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>150.0719903546772</v>
+        <v>169.6926348159986</v>
       </c>
     </row>
     <row r="209">
@@ -3558,11 +3558,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>156.0220450976014</v>
+        <v>136.2060012010795</v>
       </c>
     </row>
     <row r="210">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>168.2216933394938</v>
+        <v>145.4749115339448</v>
       </c>
     </row>
     <row r="211">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>142.4573195186641</v>
+        <v>122.4259668926803</v>
       </c>
     </row>
     <row r="212">
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>87.98069974649448</v>
+        <v>108.1882747316393</v>
       </c>
     </row>
     <row r="213">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>244.4547600179641</v>
+        <v>229.8607558359462</v>
       </c>
     </row>
     <row r="214">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>224.1347950788545</v>
+        <v>225.064995129652</v>
       </c>
     </row>
     <row r="215">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>383.9683452505717</v>
+        <v>419.672814067605</v>
       </c>
     </row>
     <row r="216">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>358.6786998752949</v>
+        <v>377.8634954661895</v>
       </c>
     </row>
     <row r="217">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>405.3050657897217</v>
+        <v>397.4782412309082</v>
       </c>
     </row>
     <row r="218">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>343.1529027900015</v>
+        <v>333.5404278771352</v>
       </c>
     </row>
     <row r="219">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>192.2969368458551</v>
+        <v>230.3482592715248</v>
       </c>
     </row>
     <row r="220">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>379.5007289420488</v>
+        <v>415.1807710422817</v>
       </c>
     </row>
     <row r="221">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>170.9482929019636</v>
+        <v>193.1966175896344</v>
       </c>
     </row>
     <row r="222">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>277.5254540437227</v>
+        <v>314.0855088794886</v>
       </c>
     </row>
     <row r="223">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>346.976523051831</v>
+        <v>384.9642702937756</v>
       </c>
     </row>
     <row r="224">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>167.7758876733445</v>
+        <v>189.8516782079799</v>
       </c>
     </row>
     <row r="225">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>405.4342490665469</v>
+        <v>396.8570901951181</v>
       </c>
     </row>
     <row r="226">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>342.2257220137689</v>
+        <v>352.345793583056</v>
       </c>
     </row>
     <row r="227">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>511.3525973892623</v>
+        <v>537.3485840089204</v>
       </c>
     </row>
     <row r="228">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>331.1662139980003</v>
+        <v>338.7538155998406</v>
       </c>
     </row>
     <row r="229">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>381.7256943903093</v>
+        <v>417.4720974985719</v>
       </c>
     </row>
     <row r="230">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>357.0246673916196</v>
+        <v>376.6730883738524</v>
       </c>
     </row>
     <row r="231">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>377.0267809314404</v>
+        <v>412.7090821028135</v>
       </c>
     </row>
     <row r="232">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>169.5897000840959</v>
+        <v>192.1475305672869</v>
       </c>
     </row>
     <row r="233">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>336.4473247808326</v>
+        <v>344.0143888267083</v>
       </c>
     </row>
     <row r="234">
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>349.4569968094802</v>
+        <v>387.4842357033926</v>
       </c>
     </row>
     <row r="235">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>223.0922603127969</v>
+        <v>224.5517052120445</v>
       </c>
     </row>
     <row r="236">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>172.9088095760513</v>
+        <v>195.3516669208213</v>
       </c>
     </row>
     <row r="237">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>378.5427318889581</v>
+        <v>414.2812049218847</v>
       </c>
     </row>
     <row r="238">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>181.6944955579513</v>
+        <v>177.962552569528</v>
       </c>
     </row>
     <row r="239">
@@ -4008,11 +4008,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>510.8703195477742</v>
+        <v>536.8344550885704</v>
       </c>
     </row>
     <row r="240">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>353.6441013146468</v>
+        <v>391.7037606540575</v>
       </c>
     </row>
     <row r="241">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>405.779922177717</v>
+        <v>397.5562571974353</v>
       </c>
     </row>
     <row r="242">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>354.4869959095565</v>
+        <v>374.2917936817031</v>
       </c>
     </row>
     <row r="243">
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>378.7680856783614</v>
+        <v>414.4853399375517</v>
       </c>
     </row>
     <row r="244">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>449.7335626017817</v>
+        <v>464.1934089637818</v>
       </c>
     </row>
     <row r="245">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>176.5776307618488</v>
+        <v>198.5647588025095</v>
       </c>
     </row>
     <row r="246">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>341.5759657726773</v>
+        <v>349.3139158828723</v>
       </c>
     </row>
     <row r="247">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>178.9192601996842</v>
+        <v>201.5696038015792</v>
       </c>
     </row>
     <row r="248">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>337.8575499479376</v>
+        <v>345.1333457202122</v>
       </c>
     </row>
     <row r="249">
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>375.1955729779149</v>
+        <v>410.8883422646456</v>
       </c>
     </row>
     <row r="250">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>414.9905506571422</v>
+        <v>408.8581684202446</v>
       </c>
     </row>
     <row r="251">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>449.8968435611127</v>
+        <v>464.582298371576</v>
       </c>
     </row>
     <row r="252">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>128.9049887187745</v>
+        <v>32.60451440507697</v>
       </c>
     </row>
     <row r="253">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>199.9453164122694</v>
+        <v>94.35960271226369</v>
       </c>
     </row>
     <row r="254">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>295.4992140148996</v>
+        <v>384.5799275406081</v>
       </c>
     </row>
     <row r="255">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>379.6069181231939</v>
+        <v>482.00735820496</v>
       </c>
     </row>
     <row r="256">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>380.258306252376</v>
+        <v>482.4906943718859</v>
       </c>
     </row>
     <row r="257">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>198.7566561597725</v>
+        <v>92.64544990077594</v>
       </c>
     </row>
     <row r="258">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>157.6723325326645</v>
+        <v>75.2899228366535</v>
       </c>
     </row>
     <row r="259">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>403.5081622823314</v>
+        <v>508.8891223415916</v>
       </c>
     </row>
     <row r="260">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>475.9405988279751</v>
+        <v>552.3573847787909</v>
       </c>
     </row>
     <row r="261">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>195.7083783065673</v>
+        <v>102.3489899239865</v>
       </c>
     </row>
     <row r="262">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>438.5077834249905</v>
+        <v>522.1664319142777</v>
       </c>
     </row>
     <row r="263">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>188.2066440310786</v>
+        <v>95.57020709971071</v>
       </c>
     </row>
     <row r="264">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>190.9071943197909</v>
+        <v>96.70476762895548</v>
       </c>
     </row>
     <row r="265">
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>405.0565056120583</v>
+        <v>510.5175932013258</v>
       </c>
     </row>
     <row r="266">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>301.8636096550673</v>
+        <v>390.1597548737963</v>
       </c>
     </row>
     <row r="267">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>198.4266612290852</v>
+        <v>92.28373519837209</v>
       </c>
     </row>
     <row r="268">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>518.4040578096872</v>
+        <v>595.7184877137429</v>
       </c>
     </row>
     <row r="269">
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>510.6400033426321</v>
+        <v>589.7659034972133</v>
       </c>
     </row>
     <row r="270">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>197.6583203948707</v>
+        <v>93.68564527290076</v>
       </c>
     </row>
     <row r="271">
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>200.1952793995961</v>
+        <v>94.17527792394209</v>
       </c>
     </row>
     <row r="272">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>215.1429120314576</v>
+        <v>112.4783746360528</v>
       </c>
     </row>
     <row r="273">
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>189.4037922176628</v>
+        <v>94.45839254828898</v>
       </c>
     </row>
     <row r="274">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>198.7324288034695</v>
+        <v>92.67265559598945</v>
       </c>
     </row>
     <row r="275">
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>215.2126130343853</v>
+        <v>112.6132028265503</v>
       </c>
     </row>
     <row r="276">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>193.0481946178191</v>
+        <v>99.02980389832064</v>
       </c>
     </row>
     <row r="277">
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>190.414855387531</v>
+        <v>97.27427688122583</v>
       </c>
     </row>
     <row r="278">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>197.1251076937621</v>
+        <v>91.50333000873195</v>
       </c>
     </row>
     <row r="279">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>189.8007120211021</v>
+        <v>95.99397161868814</v>
       </c>
     </row>
     <row r="280">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>474.2739396380379</v>
+        <v>550.7295808016556</v>
       </c>
     </row>
     <row r="281">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>106.1462563154388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>189.5541092308563</v>
+        <v>94.37343372652148</v>
       </c>
     </row>
     <row r="283">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>297.7463062317671</v>
+        <v>386.5114632433878</v>
       </c>
     </row>
     <row r="284">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>295.1508308036504</v>
+        <v>384.2393599367526</v>
       </c>
     </row>
     <row r="285">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>195.2004775661288</v>
+        <v>99.63501088455672</v>
       </c>
     </row>
     <row r="286">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>198.792485816512</v>
+        <v>92.73566034601555</v>
       </c>
     </row>
     <row r="287">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>211.7593814876636</v>
+        <v>106.8588974613416</v>
       </c>
     </row>
     <row r="288">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>409.3578444052795</v>
+        <v>515.496387359597</v>
       </c>
     </row>
     <row r="289">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>390.9140081015669</v>
+        <v>469.4482391051256</v>
       </c>
     </row>
     <row r="290">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>260.0725060296554</v>
+        <v>259.5176719658174</v>
       </c>
     </row>
     <row r="291">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>478.6929063561986</v>
+        <v>605.7632706899564</v>
       </c>
     </row>
     <row r="292">
@@ -4803,11 +4803,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>317.4733968405083</v>
+        <v>293.1002567845545</v>
       </c>
     </row>
     <row r="293">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>174.1455252776595</v>
+        <v>150.3854486811032</v>
       </c>
     </row>
     <row r="294">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>483.6949449878604</v>
+        <v>609.8136359579141</v>
       </c>
     </row>
     <row r="295">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>395.2279755294658</v>
+        <v>398.8320502782476</v>
       </c>
     </row>
     <row r="296">
@@ -4863,11 +4863,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>139.904278070824</v>
+        <v>159.1709720886669</v>
       </c>
     </row>
     <row r="297">
@@ -4878,11 +4878,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>518.017243909774</v>
+        <v>514.7670845213308</v>
       </c>
     </row>
     <row r="298">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>171.8836861734805</v>
+        <v>168.3179946113131</v>
       </c>
     </row>
     <row r="299">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>305.6066734773577</v>
+        <v>428.7166743978141</v>
       </c>
     </row>
     <row r="300">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>145.1818212920968</v>
+        <v>159.0016671290651</v>
       </c>
     </row>
     <row r="301">
@@ -4938,11 +4938,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>419.036129462474</v>
+        <v>546.1529639801837</v>
       </c>
     </row>
     <row r="302">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>407.1102990416741</v>
+        <v>533.9820761041468</v>
       </c>
     </row>
     <row r="303">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>295.353133364184</v>
+        <v>418.1241507146969</v>
       </c>
     </row>
     <row r="304">
@@ -4983,11 +4983,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>302.21659388239</v>
+        <v>423.8519858386172</v>
       </c>
     </row>
     <row r="305">
@@ -4998,11 +4998,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>299.2683693566714</v>
+        <v>421.0250492420701</v>
       </c>
     </row>
     <row r="306">
@@ -5013,11 +5013,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>265.2849324520069</v>
+        <v>264.9868752387629</v>
       </c>
     </row>
     <row r="307">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>234.1539906552349</v>
+        <v>210.2618162320152</v>
       </c>
     </row>
     <row r="308">
@@ -5043,11 +5043,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>137.9645027339064</v>
+        <v>156.6116107346159</v>
       </c>
     </row>
     <row r="309">
@@ -5058,11 +5058,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>213.5800407661942</v>
+        <v>334.4914004993488</v>
       </c>
     </row>
     <row r="310">
@@ -5073,11 +5073,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>505.864554707247</v>
+        <v>495.4572343240575</v>
       </c>
     </row>
     <row r="311">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>140.4766831106095</v>
+        <v>159.3858112034838</v>
       </c>
     </row>
     <row r="312">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>263.2808293594302</v>
+        <v>262.7876734784617</v>
       </c>
     </row>
     <row r="313">
@@ -5118,11 +5118,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>146.8970220930177</v>
+        <v>161.1344693495137</v>
       </c>
     </row>
     <row r="314">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>252.0220765832538</v>
+        <v>269.070535269441</v>
       </c>
     </row>
     <row r="315">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>290.8446586327354</v>
+        <v>302.8133964563956</v>
       </c>
     </row>
     <row r="316">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>419.8748338969282</v>
+        <v>546.9836780811395</v>
       </c>
     </row>
     <row r="317">
@@ -5178,11 +5178,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>202.3745627430987</v>
+        <v>219.3930996632319</v>
       </c>
     </row>
     <row r="318">
@@ -5193,11 +5193,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>131.3767754580934</v>
+        <v>147.6196537445319</v>
       </c>
     </row>
     <row r="319">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>405.4616480532131</v>
+        <v>532.3398390756205</v>
       </c>
     </row>
     <row r="320">
@@ -5223,11 +5223,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>257.7202175042919</v>
+        <v>378.8590788971603</v>
       </c>
     </row>
     <row r="321">
@@ -5238,11 +5238,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>299.2069770829289</v>
+        <v>421.7867030321074</v>
       </c>
     </row>
     <row r="322">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>225.2118983559744</v>
+        <v>247.9904061596499</v>
       </c>
     </row>
     <row r="323">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>233.1156151535796</v>
+        <v>209.2437086968674</v>
       </c>
     </row>
     <row r="324">
@@ -5283,11 +5283,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>174.6437031880509</v>
+        <v>171.5610975856906</v>
       </c>
     </row>
     <row r="325">
@@ -5298,11 +5298,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>258.0969226234916</v>
+        <v>278.4183922634941</v>
       </c>
     </row>
     <row r="326">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>143.4559287228808</v>
+        <v>156.8727092762293</v>
       </c>
     </row>
     <row r="327">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>298.5405184854939</v>
+        <v>419.9714842742374</v>
       </c>
     </row>
     <row r="328">
@@ -5343,11 +5343,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>291.9125166681933</v>
+        <v>413.2442366380896</v>
       </c>
     </row>
     <row r="329">
@@ -5358,11 +5358,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>201.6634020843782</v>
+        <v>177.6925516581376</v>
       </c>
     </row>
     <row r="330">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>187.3472114739193</v>
+        <v>164.433344750549</v>
       </c>
     </row>
     <row r="331">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>306.1498650987936</v>
+        <v>428.9474955583875</v>
       </c>
     </row>
     <row r="332">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>240.6553957539271</v>
+        <v>353.350985394453</v>
       </c>
     </row>
     <row r="333">
@@ -5418,11 +5418,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>305.5297858281983</v>
+        <v>427.7753898421324</v>
       </c>
     </row>
     <row r="334">
@@ -5433,11 +5433,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>265.5314730786209</v>
+        <v>264.8709808666407</v>
       </c>
     </row>
     <row r="335">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>115.8620035916273</v>
+        <v>105.7153231447665</v>
       </c>
     </row>
     <row r="336">
@@ -5463,11 +5463,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>325.2162572181462</v>
+        <v>325.683184610459</v>
       </c>
     </row>
     <row r="337">
@@ -5478,11 +5478,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>176.0201727541978</v>
+        <v>193.1659403726651</v>
       </c>
     </row>
     <row r="338">
@@ -5493,11 +5493,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>242.8334230268776</v>
+        <v>228.6386816114776</v>
       </c>
     </row>
     <row r="339">
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>262.5364558361898</v>
+        <v>239.9271333422346</v>
       </c>
     </row>
     <row r="340">
@@ -5523,11 +5523,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>244.4815171214456</v>
+        <v>234.2369337173518</v>
       </c>
     </row>
     <row r="341">
@@ -5538,11 +5538,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>249.0720943022942</v>
+        <v>226.8159864422877</v>
       </c>
     </row>
     <row r="342">
@@ -5553,11 +5553,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>130.0982456924606</v>
+        <v>3.05245814029515</v>
       </c>
     </row>
     <row r="343">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>244.7649577139401</v>
+        <v>232.7606295976149</v>
       </c>
     </row>
     <row r="344">
@@ -5583,11 +5583,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>170.4849151475579</v>
+        <v>44.63230629408451</v>
       </c>
     </row>
     <row r="345">
@@ -5598,11 +5598,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>247.3589627515343</v>
+        <v>235.6425339063696</v>
       </c>
     </row>
     <row r="346">
@@ -5613,11 +5613,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>250.7518419947306</v>
+        <v>236.3926209841623</v>
       </c>
     </row>
     <row r="347">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>245.2020554131428</v>
+        <v>228.7898553040338</v>
       </c>
     </row>
     <row r="348">
@@ -5643,11 +5643,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>247.1939855447183</v>
+        <v>238.3826140048343</v>
       </c>
     </row>
     <row r="349">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>248.9481718440073</v>
+        <v>126.9259514787582</v>
       </c>
     </row>
     <row r="350">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>262.8258537407512</v>
+        <v>240.990457513337</v>
       </c>
     </row>
     <row r="351">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>243.9905079930992</v>
+        <v>221.672979833551</v>
       </c>
     </row>
     <row r="352">
@@ -5703,11 +5703,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>245.7263957483557</v>
+        <v>123.2451849638042</v>
       </c>
     </row>
     <row r="353">
@@ -5718,11 +5718,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>241.3758450983825</v>
+        <v>232.446583431369</v>
       </c>
     </row>
     <row r="354">
@@ -5733,11 +5733,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>173.6480917764453</v>
+        <v>135.9227728142532</v>
       </c>
     </row>
     <row r="355">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>255.3696671481475</v>
+        <v>268.5129992494262</v>
       </c>
     </row>
     <row r="356">
@@ -5763,11 +5763,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>245.2199955591135</v>
+        <v>123.2245237075969</v>
       </c>
     </row>
     <row r="357">
@@ -5778,11 +5778,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>127.1680167975757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>251.8859543154234</v>
+        <v>229.2048316902433</v>
       </c>
     </row>
     <row r="359">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>244.6616573423616</v>
+        <v>229.5926036582196</v>
       </c>
     </row>
     <row r="360">
@@ -5823,11 +5823,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>242.2130875979642</v>
+        <v>231.8062255945751</v>
       </c>
     </row>
     <row r="361">
@@ -5838,11 +5838,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>184.1323231692768</v>
+        <v>254.7217919902353</v>
       </c>
     </row>
     <row r="362">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>247.2555998483565</v>
+        <v>236.9675286822333</v>
       </c>
     </row>
     <row r="363">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>248.2500861193687</v>
+        <v>236.042639746664</v>
       </c>
     </row>
     <row r="364">
@@ -5883,11 +5883,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>238.6138624870473</v>
+        <v>231.0797650168059</v>
       </c>
     </row>
     <row r="365">
@@ -5898,11 +5898,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>248.2464578486703</v>
+        <v>236.7708126174289</v>
       </c>
     </row>
     <row r="366">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>251.572927532271</v>
+        <v>130.1980141958676</v>
       </c>
     </row>
     <row r="367">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>230.4299203347763</v>
+        <v>184.798244502207</v>
       </c>
     </row>
     <row r="368">
@@ -5943,11 +5943,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>230.0711370582394</v>
+        <v>229.820113327984</v>
       </c>
     </row>
     <row r="369">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>66.73815255783093</v>
+        <v>39.15438497735472</v>
       </c>
     </row>
     <row r="370">
@@ -5973,11 +5973,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>34.52345300414044</v>
+        <v>12.57090271495102</v>
       </c>
     </row>
     <row r="371">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>317.946630304663</v>
+        <v>342.4939796860908</v>
       </c>
     </row>
     <row r="372">
@@ -6003,11 +6003,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>176.6888667503275</v>
+        <v>154.5296365267789</v>
       </c>
     </row>
     <row r="373">
@@ -6018,11 +6018,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>63.09525674037218</v>
+        <v>37.91710526660902</v>
       </c>
     </row>
     <row r="374">
@@ -6033,11 +6033,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>67.88592045568444</v>
+        <v>42.66602307691792</v>
       </c>
     </row>
     <row r="375">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>34.2181840897848</v>
+        <v>13.54667643358147</v>
       </c>
     </row>
     <row r="376">
@@ -6063,11 +6063,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>32.70858238462002</v>
+        <v>6.482501230056271</v>
       </c>
     </row>
     <row r="377">
@@ -6078,11 +6078,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>181.5158062914187</v>
+        <v>159.5564405282327</v>
       </c>
     </row>
     <row r="378">
@@ -6093,11 +6093,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>180.1765995943753</v>
+        <v>157.9057503839281</v>
       </c>
     </row>
     <row r="379">
@@ -6108,11 +6108,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>35.38984638379532</v>
+        <v>11.61629237416503</v>
       </c>
     </row>
     <row r="380">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>148.9146243709701</v>
+        <v>123.5969250984457</v>
       </c>
     </row>
     <row r="381">
@@ -6138,11 +6138,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>292.1082656735446</v>
+        <v>318.263518593437</v>
       </c>
     </row>
     <row r="382">
@@ -6153,11 +6153,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>33.3796757686011</v>
+        <v>9.701676387079416</v>
       </c>
     </row>
     <row r="383">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>31.90591786876936</v>
+        <v>7.275330297290545</v>
       </c>
     </row>
     <row r="384">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>33.24458419572206</v>
+        <v>10.61135848297473</v>
       </c>
     </row>
     <row r="385">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>63.43243743125071</v>
+        <v>38.42775221604786</v>
       </c>
     </row>
     <row r="386">
@@ -6213,11 +6213,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>293.4508617519292</v>
+        <v>319.5538914584326</v>
       </c>
     </row>
     <row r="387">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>37.08142664821583</v>
+        <v>14.41067480414424</v>
       </c>
     </row>
     <row r="388">
@@ -6243,11 +6243,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>29.33806901372546</v>
+        <v>2.798523869312165</v>
       </c>
     </row>
     <row r="389">
@@ -6258,11 +6258,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>28.37001636872408</v>
+        <v>4.086812362410984</v>
       </c>
     </row>
     <row r="390">
@@ -6273,11 +6273,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>39.11561759641163</v>
+        <v>12.82877227690499</v>
       </c>
     </row>
     <row r="391">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>203.8019484784353</v>
+        <v>184.5265200028921</v>
       </c>
     </row>
     <row r="392">
@@ -6303,11 +6303,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>31.02089893886271</v>
+        <v>4.91155522905192</v>
       </c>
     </row>
     <row r="393">
@@ -6318,11 +6318,11 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>184.6131265113243</v>
+        <v>162.3569820648295</v>
       </c>
     </row>
     <row r="394">
@@ -6333,11 +6333,11 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>27.58568935880062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_6</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>30.56895919515435</v>
+        <v>14.12354157257625</v>
       </c>
     </row>
     <row r="396">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>599.7685658275938</v>
+        <v>562.9329183211324</v>
       </c>
     </row>
     <row r="397">
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>418.910619457074</v>
+        <v>399.0386805781686</v>
       </c>
     </row>
     <row r="398">
@@ -6393,11 +6393,11 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>395.1452104601061</v>
+        <v>399.2933407902202</v>
       </c>
     </row>
     <row r="399">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>580.0655393103883</v>
+        <v>544.8395540952689</v>
       </c>
     </row>
     <row r="400">
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>419.2014824656533</v>
+        <v>404.1985816893753</v>
       </c>
     </row>
     <row r="401">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>417.7719448167981</v>
+        <v>398.0133220468219</v>
       </c>
     </row>
     <row r="402">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>290.1088194372147</v>
+        <v>271.698348756485</v>
       </c>
     </row>
     <row r="403">
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>413.7000010176697</v>
+        <v>393.8114777969823</v>
       </c>
     </row>
     <row r="404">
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>286.2644628689006</v>
+        <v>270.9129282531802</v>
       </c>
     </row>
     <row r="405">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>596.4055858326795</v>
+        <v>559.6269996577513</v>
       </c>
     </row>
     <row r="406">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>667.4815881169878</v>
+        <v>629.6244910605436</v>
       </c>
     </row>
     <row r="407">
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>418.0305093436396</v>
+        <v>398.0612564570309</v>
       </c>
     </row>
     <row r="408">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>577.1715434059126</v>
+        <v>541.9030864968256</v>
       </c>
     </row>
     <row r="409">
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>291.0608337402675</v>
+        <v>272.9139635372408</v>
       </c>
     </row>
     <row r="410">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>596.9387958350218</v>
+        <v>560.2114394204164</v>
       </c>
     </row>
     <row r="411">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>417.601541343521</v>
+        <v>397.8931264225789</v>
       </c>
     </row>
     <row r="412">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>592.2228066044695</v>
+        <v>553.9746287176301</v>
       </c>
     </row>
     <row r="413">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>316.9706336802632</v>
+        <v>290.325695922037</v>
       </c>
     </row>
     <row r="414">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>623.8236912874983</v>
+        <v>589.205834795844</v>
       </c>
     </row>
     <row r="415">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>631.3880668617128</v>
+        <v>592.9623348517237</v>
       </c>
     </row>
     <row r="416">
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>594.4100784430385</v>
+        <v>556.1763395240313</v>
       </c>
     </row>
     <row r="417">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>620.2615824043411</v>
+        <v>585.6363666275724</v>
       </c>
     </row>
     <row r="418">
@@ -6693,11 +6693,11 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>204.5305974443592</v>
+        <v>237.6201381750443</v>
       </c>
     </row>
     <row r="419">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>110.2827409697895</v>
+        <v>99.7038613045038</v>
       </c>
     </row>
     <row r="420">
@@ -6723,11 +6723,11 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>204.4596365169506</v>
+        <v>234.764391484706</v>
       </c>
     </row>
     <row r="421">
@@ -6738,11 +6738,11 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>163.7742200848483</v>
+        <v>198.7765567384305</v>
       </c>
     </row>
     <row r="422">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>208.7913962749197</v>
+        <v>237.0983883977419</v>
       </c>
     </row>
     <row r="423">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>121.5759418094487</v>
+        <v>109.2974339087442</v>
       </c>
     </row>
     <row r="424">
@@ -6783,11 +6783,11 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>213.2182452585202</v>
+        <v>243.3057882043767</v>
       </c>
     </row>
     <row r="425">
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>176.2503739454197</v>
+        <v>205.8332451562206</v>
       </c>
     </row>
     <row r="426">
@@ -6813,11 +6813,11 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>231.1188408667959</v>
+        <v>199.5832316516953</v>
       </c>
     </row>
     <row r="427">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>213.4509778017186</v>
+        <v>244.77544899438</v>
       </c>
     </row>
     <row r="428">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>181.948223952247</v>
+        <v>212.5040539822774</v>
       </c>
     </row>
     <row r="429">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>94.86397367730432</v>
+        <v>90.0980258920742</v>
       </c>
     </row>
     <row r="430">
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>100.5714524373624</v>
+        <v>93.9900122522893</v>
       </c>
     </row>
     <row r="431">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>48.39588948557887</v>
+        <v>48.06033700014402</v>
       </c>
     </row>
     <row r="432">
@@ -6903,11 +6903,11 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>463.4459507527332</v>
+        <v>462.3370152351604</v>
       </c>
     </row>
     <row r="433">
@@ -6918,11 +6918,11 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>433.5621327582323</v>
+        <v>449.9853559453078</v>
       </c>
     </row>
     <row r="434">
@@ -6933,11 +6933,11 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>229.0852832585927</v>
+        <v>162.993792613938</v>
       </c>
     </row>
     <row r="435">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>172.6159711788848</v>
+        <v>203.4341665162504</v>
       </c>
     </row>
     <row r="436">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>117.7951780549381</v>
+        <v>105.6809195503245</v>
       </c>
     </row>
     <row r="437">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>97.45745982829436</v>
+        <v>90.3683577034153</v>
       </c>
     </row>
     <row r="438">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>101.481381795035</v>
+        <v>94.08847476823729</v>
       </c>
     </row>
     <row r="439">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>510.997654198796</v>
+        <v>439.1031686450011</v>
       </c>
     </row>
     <row r="440">
@@ -7023,11 +7023,11 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>429.4902768901852</v>
+        <v>456.135414208522</v>
       </c>
     </row>
     <row r="441">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>260.2853585002077</v>
+        <v>251.7742107462432</v>
       </c>
     </row>
     <row r="442">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>208.5962880424154</v>
+        <v>242.6207437871402</v>
       </c>
     </row>
     <row r="443">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>98.25808763279977</v>
+        <v>94.55157049759576</v>
       </c>
     </row>
     <row r="444">
@@ -7083,11 +7083,11 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>208.4277253435319</v>
+        <v>239.2033432876943</v>
       </c>
     </row>
     <row r="445">
@@ -7098,11 +7098,11 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>212.3386261781216</v>
+        <v>244.7042980601115</v>
       </c>
     </row>
     <row r="446">
@@ -7113,11 +7113,11 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>209.6504118209775</v>
+        <v>238.517141078303</v>
       </c>
     </row>
     <row r="447">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>182.7667459903581</v>
+        <v>212.7492079575601</v>
       </c>
     </row>
     <row r="448">
@@ -7143,11 +7143,11 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>423.5769488863627</v>
+        <v>459.7575073825284</v>
       </c>
     </row>
     <row r="449">
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>95.67790461919937</v>
+        <v>90.29583703329229</v>
       </c>
     </row>
     <row r="450">
@@ -7173,11 +7173,11 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>484.1532863787845</v>
+        <v>480.4430992225687</v>
       </c>
     </row>
     <row r="451">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>228.5218675824255</v>
+        <v>198.0643498726504</v>
       </c>
     </row>
     <row r="452">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>102.6353178628117</v>
+        <v>97.55387968687192</v>
       </c>
     </row>
     <row r="453">
@@ -7218,11 +7218,11 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>301.0507133735346</v>
+        <v>199.5974651940966</v>
       </c>
     </row>
     <row r="454">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>386.2146034980639</v>
+        <v>335.0619337748118</v>
       </c>
     </row>
     <row r="455">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>97.23843853479993</v>
+        <v>92.01053017070051</v>
       </c>
     </row>
     <row r="456">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>102.4918480857375</v>
+        <v>95.45167583039947</v>
       </c>
     </row>
     <row r="457">
@@ -7278,11 +7278,11 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>207.4009137645875</v>
+        <v>237.9422131497212</v>
       </c>
     </row>
     <row r="458">
@@ -7293,11 +7293,11 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>428.9279411296831</v>
+        <v>454.4354598273687</v>
       </c>
     </row>
     <row r="459">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>229.5591365467445</v>
+        <v>199.2811750116876</v>
       </c>
     </row>
     <row r="460">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>175.6247251323167</v>
+        <v>206.0759102960201</v>
       </c>
     </row>
     <row r="461">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>175.3296764752763</v>
+        <v>205.4737074015495</v>
       </c>
     </row>
     <row r="462">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>51.09998502013926</v>
+        <v>50.25644795082248</v>
       </c>
     </row>
     <row r="463">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>99.97599824829125</v>
+        <v>94.34029263720771</v>
       </c>
     </row>
     <row r="464">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>168.7811319371953</v>
+        <v>199.6572089693678</v>
       </c>
     </row>
     <row r="465">
@@ -7398,11 +7398,11 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>211.6732813870892</v>
+        <v>241.6691407618989</v>
       </c>
     </row>
     <row r="466">
@@ -7413,11 +7413,11 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>232.6220725104062</v>
+        <v>202.3400634650289</v>
       </c>
     </row>
     <row r="467">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>100.092607826785</v>
+        <v>93.80687191812108</v>
       </c>
     </row>
     <row r="468">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>96.94585824993405</v>
+        <v>91.55369369176938</v>
       </c>
     </row>
     <row r="469">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>178.0547726996159</v>
+        <v>207.7644881052486</v>
       </c>
     </row>
     <row r="470">
@@ -7473,11 +7473,11 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>209.6007710482695</v>
+        <v>240.297222012738</v>
       </c>
     </row>
     <row r="471">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>217.769738655443</v>
+        <v>248.1144254000412</v>
       </c>
     </row>
     <row r="472">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>102.700602997662</v>
+        <v>94.17249277637561</v>
       </c>
     </row>
     <row r="473">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>172.7706883374275</v>
+        <v>203.1957489360825</v>
       </c>
     </row>
     <row r="474">
@@ -7533,11 +7533,11 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>429.3340900803877</v>
+        <v>455.2583033426945</v>
       </c>
     </row>
     <row r="475">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>99.365783649566</v>
+        <v>91.13841375349979</v>
       </c>
     </row>
     <row r="476">
@@ -7563,11 +7563,11 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>426.3835440125061</v>
+        <v>458.674922905298</v>
       </c>
     </row>
     <row r="477">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>178.0194198959729</v>
+        <v>208.7746257080976</v>
       </c>
     </row>
     <row r="478">
@@ -7593,11 +7593,11 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>208.9435669676058</v>
+        <v>241.1319183450053</v>
       </c>
     </row>
     <row r="479">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>178.8457234807114</v>
+        <v>208.8093372115301</v>
       </c>
     </row>
     <row r="480">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>107.3145602966586</v>
+        <v>98.09423920156364</v>
       </c>
     </row>
     <row r="481">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>78.34448568653632</v>
+        <v>83.86170948034218</v>
       </c>
     </row>
     <row r="482">
@@ -7653,11 +7653,11 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>494.2465546328309</v>
+        <v>451.2518729527299</v>
       </c>
     </row>
     <row r="483">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>208.6719006944995</v>
+        <v>205.0075027925476</v>
       </c>
     </row>
     <row r="484">
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>173.0380180324195</v>
+        <v>204.411680816876</v>
       </c>
     </row>
     <row r="485">
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>306.8243085037814</v>
+        <v>342.6902945712899</v>
       </c>
     </row>
     <row r="486">
@@ -7713,11 +7713,11 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>509.5008732297528</v>
+        <v>436.7125282091822</v>
       </c>
     </row>
     <row r="487">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>163.7335498059527</v>
+        <v>75.4651024189595</v>
       </c>
     </row>
     <row r="488">
@@ -7743,11 +7743,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>482.7255904190506</v>
+        <v>478.9435636984282</v>
       </c>
     </row>
     <row r="489">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>176.3452400412433</v>
+        <v>206.7994832782831</v>
       </c>
     </row>
     <row r="490">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>96.72437721924653</v>
+        <v>93.00717953846529</v>
       </c>
     </row>
     <row r="491">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>482.017426840228</v>
+        <v>478.129089313604</v>
       </c>
     </row>
     <row r="492">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>228.9300086027407</v>
+        <v>262.869810262483</v>
       </c>
     </row>
     <row r="493">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>144.5352295904483</v>
+        <v>173.614929625572</v>
       </c>
     </row>
     <row r="494">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>304.1258562519051</v>
+        <v>340.0263864003297</v>
       </c>
     </row>
     <row r="495">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>176.328593549544</v>
+        <v>206.5414340971641</v>
       </c>
     </row>
     <row r="496">
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>345.6396454305997</v>
+        <v>334.3077432722394</v>
       </c>
     </row>
     <row r="497">
@@ -7878,11 +7878,11 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>204.2468831622038</v>
+        <v>265.9757361101167</v>
       </c>
     </row>
     <row r="498">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>78.46596702303529</v>
+        <v>40.28803578428388</v>
       </c>
     </row>
     <row r="499">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>38.42670238202552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>228.1579527766796</v>
+        <v>198.4169489828125</v>
       </c>
     </row>
     <row r="501">
@@ -7938,11 +7938,11 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>229.1174983035737</v>
+        <v>197.2457940055387</v>
       </c>
     </row>
     <row r="502">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>121.9724126682299</v>
+        <v>114.9391757734247</v>
       </c>
     </row>
     <row r="503">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>229.178044449383</v>
+        <v>199.1949041175324</v>
       </c>
     </row>
     <row r="504">
@@ -7983,11 +7983,11 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>DC_6</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>216.9896041973278</v>
+        <v>212.3623313996765</v>
       </c>
     </row>
     <row r="505">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>112.4827109906133</v>
+        <v>98.10985974597351</v>
       </c>
     </row>
   </sheetData>

--- a/store_dc_distances.xlsx
+++ b/store_dc_distances.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -513,7 +513,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -618,7 +618,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -873,7 +873,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -933,7 +933,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DC_4</t>
+          <t>DC_1</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>DC_5</t>
+          <t>DC_3</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>449.9853559453078</v>
+        <v>465.8953011676563</v>
       </c>
     </row>
     <row r="434">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>456.135414208522</v>
+        <v>462.1981527260011</v>
       </c>
     </row>
     <row r="441">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>459.7575073825284</v>
+        <v>455.943847080418</v>
       </c>
     </row>
     <row r="449">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>454.4354598273687</v>
+        <v>461.2613982587158</v>
       </c>
     </row>
     <row r="459">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>455.2583033426945</v>
+        <v>461.8776223578468</v>
       </c>
     </row>
     <row r="475">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>458.674922905298</v>
+        <v>459.0257982920651</v>
       </c>
     </row>
     <row r="477">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>451.2518729527299</v>
+        <v>506.1233495929659</v>
       </c>
     </row>
     <row r="483">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>DC_1</t>
+          <t>DC_4</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>DC_2</t>
+          <t>DC_5</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>DC_3</t>
+          <t>DC_2</t>
         </is>
       </c>
       <c r="C505" t="n">
